--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
@@ -250,6 +250,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -266,7 +267,6 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -900,7 +900,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Em Simulador, escolha o procedimento e digite o valor de tabela de cada pagador (o particular é o preço praticado). Leia o quadro 2 (agenda cheia): margem, líquido por hora e o veredito de cada pagador.</t>
+          <t>Em Simulador, escolha o procedimento e copie o valor de tabela de cada pagador da planilha 08 · Tabela de preços (o particular é o preço praticado). A 08 é a fonte única da tabela no kit: mudou um preço, atualize 08 → 06 → 07 → 01, nessa ordem. Leia o quadro 2 (agenda cheia): margem, líquido por hora e o veredito de cada pagador.</t>
         </is>
       </c>
     </row>
@@ -1151,89 +1151,94 @@
           <t>Consulta</t>
         </is>
       </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Os valores de tabela do quadro 2 saem da planilha 08 · Tabela de preços (a fonte única da tabela no kit): copie de lá, não digite um preço diferente aqui.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Minutos</t>
         </is>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="24">
         <f>IFERROR(INDEX(Config!$B$19:$B$30,MATCH(B8,Config!$A$19:$A$30,0)),"")</f>
         <v>30</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Gera retorno?</t>
         </is>
       </c>
-      <c r="B10" s="24" t="str">
+      <c r="B10" s="25" t="str">
         <f>IFERROR(INDEX(Config!$C$19:$C$30,MATCH(B8,Config!$A$19:$A$30,0)),"")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>Material (R$)</t>
         </is>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="26">
         <f>IFERROR(INDEX(Config!$D$19:$D$30,MATCH(B8,Config!$A$19:$A$30,0)),0)</f>
         <v>4</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>Tempo com retorno embutido (min)</t>
         </is>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <f>IF(B9="","",B9+IF(B10="Sim",Config!$E$19*Config!$F$19,0))</f>
         <v>38</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>Custo cheio do atendimento (R$)</t>
         </is>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="28">
         <f>IF(B12="","",B12/60*Config!$B$5+B11)</f>
         <v>130.666666666667</v>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Tempo (com retorno) ÷ 60 × custo-hora + material. É o custo com a estrutura inteira rateada: a leitura de agenda cheia.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>Hora mínima a cobrar (R$)</t>
         </is>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="26">
         <f>IFERROR(Config!$B$5/(1-Config!$B$6-Config!$B$7),"")</f>
         <v>338.983050847458</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>Preço mínimo deste procedimento (R$)</t>
         </is>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="28">
         <f>IF(B13="","",IFERROR(B13/(1-Config!$B$6-Config!$B$7),""))</f>
         <v>221.468926553672</v>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>Custo cheio ÷ (1 − impostos − margem mínima). O mesmo número da planilha 06.</t>
         </is>
@@ -1327,7 +1332,7 @@
       <c r="B19" s="31" t="n">
         <v>380</v>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="24">
         <f>IF(Config!$A$10="","",Config!$B$10)</f>
         <v>0</v>
       </c>
@@ -1335,27 +1340,27 @@
         <f>IF(Config!$A$10="","",Config!$C$10)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="26">
         <f>IF(OR(Config!$A$10="",B19=""),"",B19*(1-D19))</f>
         <v>380</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="26">
         <f>IF(E19="","",E19*Config!$B$8*C19/30)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="26">
         <f>IF(E19="","",E19*Config!$B$6)</f>
         <v>41.8</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="28">
         <f>IF(E19="","",E19-F19-G19)</f>
         <v>338.2</v>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="26">
         <f>IF(E19="","",$B$13)</f>
         <v>130.666666666667</v>
       </c>
-      <c r="J19" s="25">
+      <c r="J19" s="26">
         <f>IF(E19="","",H19-I19)</f>
         <v>207.533333333333</v>
       </c>
@@ -1363,7 +1368,7 @@
         <f>IF(OR(E19="",B19=0),"",J19/B19)</f>
         <v>0.546140350877193</v>
       </c>
-      <c r="L19" s="25">
+      <c r="L19" s="26">
         <f>IF(OR(E19="",$B$12=0),"",H19/($B$12/60))</f>
         <v>534</v>
       </c>
@@ -1384,7 +1389,7 @@
       <c r="B20" s="31" t="n">
         <v>120</v>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="24">
         <f>IF(Config!$A$11="","",Config!$B$11)</f>
         <v>30</v>
       </c>
@@ -1392,27 +1397,27 @@
         <f>IF(Config!$A$11="","",Config!$C$11)</f>
         <v>0.03</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="26">
         <f>IF(OR(Config!$A$11="",B20=""),"",B20*(1-D20))</f>
         <v>116.4</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="26">
         <f>IF(E20="","",E20*Config!$B$8*C20/30)</f>
         <v>1.746</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="26">
         <f>IF(E20="","",E20*Config!$B$6)</f>
         <v>12.804</v>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="28">
         <f>IF(E20="","",E20-F20-G20)</f>
         <v>101.85</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="26">
         <f>IF(E20="","",$B$13)</f>
         <v>130.666666666667</v>
       </c>
-      <c r="J20" s="25">
+      <c r="J20" s="26">
         <f>IF(E20="","",H20-I20)</f>
         <v>-28.8166666666667</v>
       </c>
@@ -1420,7 +1425,7 @@
         <f>IF(OR(E20="",B20=0),"",J20/B20)</f>
         <v>-0.240138888888889</v>
       </c>
-      <c r="L20" s="25">
+      <c r="L20" s="26">
         <f>IF(OR(E20="",$B$12=0),"",H20/($B$12/60))</f>
         <v>160.815789473684</v>
       </c>
@@ -1441,7 +1446,7 @@
       <c r="B21" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="24">
         <f>IF(Config!$A$12="","",Config!$B$12)</f>
         <v>45</v>
       </c>
@@ -1449,27 +1454,27 @@
         <f>IF(Config!$A$12="","",Config!$C$12)</f>
         <v>0.06</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="26">
         <f>IF(OR(Config!$A$12="",B21=""),"",B21*(1-D21))</f>
         <v>94</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="26">
         <f>IF(E21="","",E21*Config!$B$8*C21/30)</f>
         <v>2.115</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="26">
         <f>IF(E21="","",E21*Config!$B$6)</f>
         <v>10.34</v>
       </c>
-      <c r="H21" s="27">
+      <c r="H21" s="28">
         <f>IF(E21="","",E21-F21-G21)</f>
         <v>81.545</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="26">
         <f>IF(E21="","",$B$13)</f>
         <v>130.666666666667</v>
       </c>
-      <c r="J21" s="25">
+      <c r="J21" s="26">
         <f>IF(E21="","",H21-I21)</f>
         <v>-49.1216666666667</v>
       </c>
@@ -1477,7 +1482,7 @@
         <f>IF(OR(E21="",B21=0),"",J21/B21)</f>
         <v>-0.491216666666667</v>
       </c>
-      <c r="L21" s="25">
+      <c r="L21" s="26">
         <f>IF(OR(E21="",$B$12=0),"",H21/($B$12/60))</f>
         <v>128.755263157895</v>
       </c>
@@ -1498,7 +1503,7 @@
       <c r="B22" s="31" t="n">
         <v>90</v>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="24">
         <f>IF(Config!$A$13="","",Config!$B$13)</f>
         <v>60</v>
       </c>
@@ -1506,27 +1511,27 @@
         <f>IF(Config!$A$13="","",Config!$C$13)</f>
         <v>0.1</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="26">
         <f>IF(OR(Config!$A$13="",B22=""),"",B22*(1-D22))</f>
         <v>81</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="26">
         <f>IF(E22="","",E22*Config!$B$8*C22/30)</f>
         <v>2.43</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="26">
         <f>IF(E22="","",E22*Config!$B$6)</f>
         <v>8.91</v>
       </c>
-      <c r="H22" s="27">
+      <c r="H22" s="28">
         <f>IF(E22="","",E22-F22-G22)</f>
         <v>69.66</v>
       </c>
-      <c r="I22" s="25">
+      <c r="I22" s="26">
         <f>IF(E22="","",$B$13)</f>
         <v>130.666666666667</v>
       </c>
-      <c r="J22" s="25">
+      <c r="J22" s="26">
         <f>IF(E22="","",H22-I22)</f>
         <v>-61.0066666666667</v>
       </c>
@@ -1534,7 +1539,7 @@
         <f>IF(OR(E22="",B22=0),"",J22/B22)</f>
         <v>-0.677851851851852</v>
       </c>
-      <c r="L22" s="25">
+      <c r="L22" s="26">
         <f>IF(OR(E22="",$B$12=0),"",H22/($B$12/60))</f>
         <v>109.989473684211</v>
       </c>
@@ -1553,7 +1558,7 @@
         <v/>
       </c>
       <c r="B23" s="31" t="n"/>
-      <c r="C23" s="23">
+      <c r="C23" s="24">
         <f>IF(Config!$A$14="","",Config!$B$14)</f>
         <v/>
       </c>
@@ -1561,27 +1566,27 @@
         <f>IF(Config!$A$14="","",Config!$C$14)</f>
         <v/>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="26">
         <f>IF(OR(Config!$A$14="",B23=""),"",B23*(1-D23))</f>
         <v/>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="26">
         <f>IF(E23="","",E23*Config!$B$8*C23/30)</f>
         <v/>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="26">
         <f>IF(E23="","",E23*Config!$B$6)</f>
         <v/>
       </c>
-      <c r="H23" s="27">
+      <c r="H23" s="28">
         <f>IF(E23="","",E23-F23-G23)</f>
         <v/>
       </c>
-      <c r="I23" s="25">
+      <c r="I23" s="26">
         <f>IF(E23="","",$B$13)</f>
         <v/>
       </c>
-      <c r="J23" s="25">
+      <c r="J23" s="26">
         <f>IF(E23="","",H23-I23)</f>
         <v/>
       </c>
@@ -1589,7 +1594,7 @@
         <f>IF(OR(E23="",B23=0),"",J23/B23)</f>
         <v/>
       </c>
-      <c r="L23" s="25">
+      <c r="L23" s="26">
         <f>IF(OR(E23="",$B$12=0),"",H23/($B$12/60))</f>
         <v/>
       </c>
@@ -1608,7 +1613,7 @@
         <v/>
       </c>
       <c r="B24" s="31" t="n"/>
-      <c r="C24" s="23">
+      <c r="C24" s="24">
         <f>IF(Config!$A$15="","",Config!$B$15)</f>
         <v/>
       </c>
@@ -1616,27 +1621,27 @@
         <f>IF(Config!$A$15="","",Config!$C$15)</f>
         <v/>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="26">
         <f>IF(OR(Config!$A$15="",B24=""),"",B24*(1-D24))</f>
         <v/>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="26">
         <f>IF(E24="","",E24*Config!$B$8*C24/30)</f>
         <v/>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="26">
         <f>IF(E24="","",E24*Config!$B$6)</f>
         <v/>
       </c>
-      <c r="H24" s="27">
+      <c r="H24" s="28">
         <f>IF(E24="","",E24-F24-G24)</f>
         <v/>
       </c>
-      <c r="I24" s="25">
+      <c r="I24" s="26">
         <f>IF(E24="","",$B$13)</f>
         <v/>
       </c>
-      <c r="J24" s="25">
+      <c r="J24" s="26">
         <f>IF(E24="","",H24-I24)</f>
         <v/>
       </c>
@@ -1644,7 +1649,7 @@
         <f>IF(OR(E24="",B24=0),"",J24/B24)</f>
         <v/>
       </c>
-      <c r="L24" s="25">
+      <c r="L24" s="26">
         <f>IF(OR(E24="",$B$12=0),"",H24/($B$12/60))</f>
         <v/>
       </c>
@@ -1674,7 +1679,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>Com agenda vazia o custo fixo já está pago: o que importa é a contribuição (líquido − material). Com agenda cheia, cada horário de convênio toma o lugar de um particular, e vale a leitura do quadro 2.</t>
         </is>
@@ -1722,23 +1727,23 @@
         <f>A19</f>
         <v>Particular</v>
       </c>
-      <c r="B31" s="25">
+      <c r="B31" s="26">
         <f>IF(H19="","",H19)</f>
         <v>338.2</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="26">
         <f>IF(H19="","",$B$11)</f>
         <v>4</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="28">
         <f>IF(B31="","",B31-C31)</f>
         <v>334.2</v>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="26">
         <f>IF(OR(D31="",$B$12=0),"",D31/($B$12/60))</f>
         <v>527.684210526316</v>
       </c>
-      <c r="F31" s="26">
+      <c r="F31" s="27">
         <f>IF(OR(D31="",D31&lt;=0,$D$31=""),"",$D$31/D31)</f>
         <v>1</v>
       </c>
@@ -1752,23 +1757,23 @@
         <f>A20</f>
         <v>Saúde Total</v>
       </c>
-      <c r="B32" s="25">
+      <c r="B32" s="26">
         <f>IF(H20="","",H20)</f>
         <v>101.85</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="26">
         <f>IF(H20="","",$B$11)</f>
         <v>4</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="28">
         <f>IF(B32="","",B32-C32)</f>
         <v>97.85</v>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="26">
         <f>IF(OR(D32="",$B$12=0),"",D32/($B$12/60))</f>
         <v>154.5</v>
       </c>
-      <c r="F32" s="26">
+      <c r="F32" s="27">
         <f>IF(OR(D32="",D32&lt;=0,$D$31=""),"",$D$31/D32)</f>
         <v>3.41543178334185</v>
       </c>
@@ -1782,23 +1787,23 @@
         <f>A21</f>
         <v>MediPlan</v>
       </c>
-      <c r="B33" s="25">
+      <c r="B33" s="26">
         <f>IF(H21="","",H21)</f>
         <v>81.545</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="26">
         <f>IF(H21="","",$B$11)</f>
         <v>4</v>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="28">
         <f>IF(B33="","",B33-C33)</f>
         <v>77.545</v>
       </c>
-      <c r="E33" s="25">
+      <c r="E33" s="26">
         <f>IF(OR(D33="",$B$12=0),"",D33/($B$12/60))</f>
         <v>122.439473684211</v>
       </c>
-      <c r="F33" s="26">
+      <c r="F33" s="27">
         <f>IF(OR(D33="",D33&lt;=0,$D$31=""),"",$D$31/D33)</f>
         <v>4.30975562576569</v>
       </c>
@@ -1812,23 +1817,23 @@
         <f>A22</f>
         <v>Vida Care</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="26">
         <f>IF(H22="","",H22)</f>
         <v>69.66</v>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="26">
         <f>IF(H22="","",$B$11)</f>
         <v>4</v>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="28">
         <f>IF(B34="","",B34-C34)</f>
         <v>65.66</v>
       </c>
-      <c r="E34" s="25">
+      <c r="E34" s="26">
         <f>IF(OR(D34="",$B$12=0),"",D34/($B$12/60))</f>
         <v>103.673684210526</v>
       </c>
-      <c r="F34" s="26">
+      <c r="F34" s="27">
         <f>IF(OR(D34="",D34&lt;=0,$D$31=""),"",$D$31/D34)</f>
         <v>5.08985683825769</v>
       </c>
@@ -1842,23 +1847,23 @@
         <f>A23</f>
         <v/>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="26">
         <f>IF(H23="","",H23)</f>
         <v/>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="26">
         <f>IF(H23="","",$B$11)</f>
         <v/>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="28">
         <f>IF(B35="","",B35-C35)</f>
         <v/>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="26">
         <f>IF(OR(D35="",$B$12=0),"",D35/($B$12/60))</f>
         <v/>
       </c>
-      <c r="F35" s="26">
+      <c r="F35" s="27">
         <f>IF(OR(D35="",D35&lt;=0,$D$31=""),"",$D$31/D35)</f>
         <v/>
       </c>
@@ -1872,23 +1877,23 @@
         <f>A24</f>
         <v/>
       </c>
-      <c r="B36" s="25">
+      <c r="B36" s="26">
         <f>IF(H24="","",H24)</f>
         <v/>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="26">
         <f>IF(H24="","",$B$11)</f>
         <v/>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="28">
         <f>IF(B36="","",B36-C36)</f>
         <v/>
       </c>
-      <c r="E36" s="25">
+      <c r="E36" s="26">
         <f>IF(OR(D36="",$B$12=0),"",D36/($B$12/60))</f>
         <v/>
       </c>
-      <c r="F36" s="26">
+      <c r="F36" s="27">
         <f>IF(OR(D36="",D36&lt;=0,$D$31=""),"",$D$31/D36)</f>
         <v/>
       </c>
@@ -1898,7 +1903,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="28" t="inlineStr">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>"Atendimentos = 1 particular": quantos atendimentos deste pagador rendem a contribuição de um particular. Compare com as horas vazias do mês (Painel da 01) antes de aceitar ou descredenciar um convênio.</t>
         </is>
@@ -1914,7 +1919,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="28" t="inlineStr">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>Amarelo: quantos atendimentos de cada pagador no mês (no exemplo, as consultas realizadas em agosto de 2026, Painel da 01 por pagador). A planilha soma o líquido, o custo cheio e o resultado.</t>
         </is>
@@ -2184,7 +2189,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="28" t="inlineStr">
+      <c r="A50" s="22" t="inlineStr">
         <is>
           <t>Resultado negativo num pagador e positivo no total é a situação comum: o particular sustenta o convênio. Pergunta certa: o convênio traz pacientes que virariam particulares ou exames? Se não, negocie a tabela ou reduza os horários dele.</t>
         </is>
@@ -2192,7 +2197,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="C15:J15"/>
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="C5:D5"/>
@@ -2212,6 +2217,7 @@
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A7:J7"/>
+    <mergeCell ref="C8:J8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="A29:N29"/>
@@ -2324,7 +2330,7 @@
       <c r="B5" s="44" t="n">
         <v>200</v>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>Copie do Painel da planilha 05. No exemplo, R$ 200,00.</t>
         </is>
@@ -2333,15 +2339,15 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>Impostos e taxas sobre o que entra (%)</t>
+          <t>Impostos sobre o que entra (%)</t>
         </is>
       </c>
       <c r="B6" s="45" t="n">
         <v>0.11</v>
       </c>
-      <c r="C6" s="28" t="inlineStr">
-        <is>
-          <t>A mesma alíquota efetiva das planilhas 05 e 06 (exemplo: 11 %).</t>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>A mesma alíquota efetiva das planilhas 05 e 06 (exemplo: 11 %). Só imposto: a taxa da maquininha não entra aqui (o convênio não passa na maquininha; o cartão é conciliado na 16).</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2360,7 @@
       <c r="B7" s="45" t="n">
         <v>0.3</v>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>A mesma margem mínima da 05 e da 06.</t>
         </is>
@@ -2369,7 +2375,7 @@
       <c r="B8" s="46" t="n">
         <v>0.015</v>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>O que custa esperar 30, 45 ou 60 dias pelo dinheiro: juros do cheque especial ou da antecipação, ou o rendimento que o dinheiro parado deixa de dar. 1,5 % ao mês é um exemplo; use o seu.</t>
         </is>
@@ -2482,7 +2488,7 @@
       <c r="D15" s="21" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>Preencha de cima para baixo, sem pular linha. Glosa esperada: quanto o convênio costuma não pagar do que foi enviado (Painel da planilha 13, por convênio). Prazo: dias entre o envio do lote e o pagamento.</t>
         </is>
@@ -2561,7 +2567,7 @@
       <c r="D20" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>Só na primeira linha: valem para todos os procedimentos que geram retorno (iguais à planilha 06).</t>
         </is>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
@@ -18,14 +18,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
-    <numFmt numFmtId="169" formatCode="+0%;-0%;0%"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0"/>
+  <numFmts count="8">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+    <numFmt numFmtId="170" formatCode="+0%;-0%;0%"/>
+    <numFmt numFmtId="171" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -231,10 +232,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -258,30 +259,30 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -291,26 +292,26 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -318,7 +319,7 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -847,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1008,17 +1009,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -2316,9 +2329,8 @@
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B4" s="43">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B4" s="43" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="5">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
@@ -997,7 +997,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="B13" s="28">
-        <f>IF(B12="","",B12/60*Config!$B$5+B11)</f>
+        <f>IF(B12="","",IF(NOT(ISNUMBER(Config!$B$5)),"falta o custo-hora em Config",B12/60*Config!$B$5+B11))</f>
         <v>130.666666666667</v>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B14" s="26">
-        <f>IFERROR(Config!$B$5/(1-Config!$B$6-Config!$B$7),"")</f>
+        <f>IF(NOT(ISNUMBER(Config!$B$5)),"falta o custo-hora em Config",IF(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE),Config!$B$5/(1-Config!$B$6-Config!$B$7),"margens inválidas (Config)"))</f>
         <v>338.983050847458</v>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="B15" s="28">
-        <f>IF(B13="","",IFERROR(B13/(1-Config!$B$6-Config!$B$7),""))</f>
+        <f>IF(B13="","",IF(NOT(ISNUMBER(B13)),B13,IF(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE),B13/(1-Config!$B$6-Config!$B$7),"margens inválidas (Config)")))</f>
         <v>221.468926553672</v>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -1362,11 +1362,11 @@
         <v>0</v>
       </c>
       <c r="G19" s="26">
-        <f>IF(E19="","",E19*Config!$B$6)</f>
+        <f>IF(OR(E19="",NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E19*Config!$B$6)</f>
         <v>41.8</v>
       </c>
       <c r="H19" s="28">
-        <f>IF(E19="","",E19-F19-G19)</f>
+        <f>IF(OR(E19="",NOT(ISNUMBER(G19))),"",E19-F19-G19)</f>
         <v>338.2</v>
       </c>
       <c r="I19" s="26">
@@ -1374,23 +1374,23 @@
         <v>130.666666666667</v>
       </c>
       <c r="J19" s="26">
-        <f>IF(E19="","",H19-I19)</f>
+        <f>IF(OR(NOT(ISNUMBER(H19)),NOT(ISNUMBER(I19))),"",H19-I19)</f>
         <v>207.533333333333</v>
       </c>
       <c r="K19" s="33">
-        <f>IF(OR(E19="",B19=0),"",J19/B19)</f>
+        <f>IF(OR(NOT(ISNUMBER(J19)),N(B19)=0),"",J19/B19)</f>
         <v>0.546140350877193</v>
       </c>
       <c r="L19" s="26">
-        <f>IF(OR(E19="",$B$12=0),"",H19/($B$12/60))</f>
+        <f>IF(OR(NOT(ISNUMBER(H19)),N($B$12)=0),"",H19/($B$12/60))</f>
         <v>534</v>
       </c>
       <c r="M19" s="34">
-        <f>IF(L19="","",L19/$B$14-1)</f>
+        <f>IF(OR(L19="",NOT(ISNUMBER($B$14))),"",L19/$B$14-1)</f>
         <v>0.5753</v>
       </c>
       <c r="N19" s="30" t="str">
-        <f>IF(E19="","",IF(J19&lt;0,"Não cobre o custo cheio",IF(K19&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))</f>
+        <f>IF(E19="","",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I19)),"Falta o custo-hora em Config",IF(J19&lt;0,"Não cobre o custo cheio",IF(K19&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))))</f>
         <v>Cobre custo e margem</v>
       </c>
     </row>
@@ -1419,11 +1419,11 @@
         <v>1.746</v>
       </c>
       <c r="G20" s="26">
-        <f>IF(E20="","",E20*Config!$B$6)</f>
+        <f>IF(OR(E20="",NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E20*Config!$B$6)</f>
         <v>12.804</v>
       </c>
       <c r="H20" s="28">
-        <f>IF(E20="","",E20-F20-G20)</f>
+        <f>IF(OR(E20="",NOT(ISNUMBER(G20))),"",E20-F20-G20)</f>
         <v>101.85</v>
       </c>
       <c r="I20" s="26">
@@ -1431,23 +1431,23 @@
         <v>130.666666666667</v>
       </c>
       <c r="J20" s="26">
-        <f>IF(E20="","",H20-I20)</f>
+        <f>IF(OR(NOT(ISNUMBER(H20)),NOT(ISNUMBER(I20))),"",H20-I20)</f>
         <v>-28.8166666666667</v>
       </c>
       <c r="K20" s="33">
-        <f>IF(OR(E20="",B20=0),"",J20/B20)</f>
+        <f>IF(OR(NOT(ISNUMBER(J20)),N(B20)=0),"",J20/B20)</f>
         <v>-0.240138888888889</v>
       </c>
       <c r="L20" s="26">
-        <f>IF(OR(E20="",$B$12=0),"",H20/($B$12/60))</f>
+        <f>IF(OR(NOT(ISNUMBER(H20)),N($B$12)=0),"",H20/($B$12/60))</f>
         <v>160.815789473684</v>
       </c>
       <c r="M20" s="34">
-        <f>IF(L20="","",L20/$B$14-1)</f>
+        <f>IF(OR(L20="",NOT(ISNUMBER($B$14))),"",L20/$B$14-1)</f>
         <v>-0.525593421052632</v>
       </c>
       <c r="N20" s="30" t="str">
-        <f>IF(E20="","",IF(J20&lt;0,"Não cobre o custo cheio",IF(K20&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))</f>
+        <f>IF(E20="","",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I20)),"Falta o custo-hora em Config",IF(J20&lt;0,"Não cobre o custo cheio",IF(K20&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))))</f>
         <v>Não cobre o custo cheio</v>
       </c>
     </row>
@@ -1476,11 +1476,11 @@
         <v>2.115</v>
       </c>
       <c r="G21" s="26">
-        <f>IF(E21="","",E21*Config!$B$6)</f>
+        <f>IF(OR(E21="",NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E21*Config!$B$6)</f>
         <v>10.34</v>
       </c>
       <c r="H21" s="28">
-        <f>IF(E21="","",E21-F21-G21)</f>
+        <f>IF(OR(E21="",NOT(ISNUMBER(G21))),"",E21-F21-G21)</f>
         <v>81.545</v>
       </c>
       <c r="I21" s="26">
@@ -1488,23 +1488,23 @@
         <v>130.666666666667</v>
       </c>
       <c r="J21" s="26">
-        <f>IF(E21="","",H21-I21)</f>
+        <f>IF(OR(NOT(ISNUMBER(H21)),NOT(ISNUMBER(I21))),"",H21-I21)</f>
         <v>-49.1216666666667</v>
       </c>
       <c r="K21" s="33">
-        <f>IF(OR(E21="",B21=0),"",J21/B21)</f>
+        <f>IF(OR(NOT(ISNUMBER(J21)),N(B21)=0),"",J21/B21)</f>
         <v>-0.491216666666667</v>
       </c>
       <c r="L21" s="26">
-        <f>IF(OR(E21="",$B$12=0),"",H21/($B$12/60))</f>
+        <f>IF(OR(NOT(ISNUMBER(H21)),N($B$12)=0),"",H21/($B$12/60))</f>
         <v>128.755263157895</v>
       </c>
       <c r="M21" s="34">
-        <f>IF(L21="","",L21/$B$14-1)</f>
+        <f>IF(OR(L21="",NOT(ISNUMBER($B$14))),"",L21/$B$14-1)</f>
         <v>-0.62017197368421</v>
       </c>
       <c r="N21" s="30" t="str">
-        <f>IF(E21="","",IF(J21&lt;0,"Não cobre o custo cheio",IF(K21&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))</f>
+        <f>IF(E21="","",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I21)),"Falta o custo-hora em Config",IF(J21&lt;0,"Não cobre o custo cheio",IF(K21&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))))</f>
         <v>Não cobre o custo cheio</v>
       </c>
     </row>
@@ -1533,11 +1533,11 @@
         <v>2.43</v>
       </c>
       <c r="G22" s="26">
-        <f>IF(E22="","",E22*Config!$B$6)</f>
+        <f>IF(OR(E22="",NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E22*Config!$B$6)</f>
         <v>8.91</v>
       </c>
       <c r="H22" s="28">
-        <f>IF(E22="","",E22-F22-G22)</f>
+        <f>IF(OR(E22="",NOT(ISNUMBER(G22))),"",E22-F22-G22)</f>
         <v>69.66</v>
       </c>
       <c r="I22" s="26">
@@ -1545,23 +1545,23 @@
         <v>130.666666666667</v>
       </c>
       <c r="J22" s="26">
-        <f>IF(E22="","",H22-I22)</f>
+        <f>IF(OR(NOT(ISNUMBER(H22)),NOT(ISNUMBER(I22))),"",H22-I22)</f>
         <v>-61.0066666666667</v>
       </c>
       <c r="K22" s="33">
-        <f>IF(OR(E22="",B22=0),"",J22/B22)</f>
+        <f>IF(OR(NOT(ISNUMBER(J22)),N(B22)=0),"",J22/B22)</f>
         <v>-0.677851851851852</v>
       </c>
       <c r="L22" s="26">
-        <f>IF(OR(E22="",$B$12=0),"",H22/($B$12/60))</f>
+        <f>IF(OR(NOT(ISNUMBER(H22)),N($B$12)=0),"",H22/($B$12/60))</f>
         <v>109.989473684211</v>
       </c>
       <c r="M22" s="34">
-        <f>IF(L22="","",L22/$B$14-1)</f>
+        <f>IF(OR(L22="",NOT(ISNUMBER($B$14))),"",L22/$B$14-1)</f>
         <v>-0.675531052631579</v>
       </c>
       <c r="N22" s="30" t="str">
-        <f>IF(E22="","",IF(J22&lt;0,"Não cobre o custo cheio",IF(K22&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))</f>
+        <f>IF(E22="","",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I22)),"Falta o custo-hora em Config",IF(J22&lt;0,"Não cobre o custo cheio",IF(K22&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))))</f>
         <v>Não cobre o custo cheio</v>
       </c>
     </row>
@@ -1588,11 +1588,11 @@
         <v/>
       </c>
       <c r="G23" s="26">
-        <f>IF(E23="","",E23*Config!$B$6)</f>
+        <f>IF(OR(E23="",NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E23*Config!$B$6)</f>
         <v/>
       </c>
       <c r="H23" s="28">
-        <f>IF(E23="","",E23-F23-G23)</f>
+        <f>IF(OR(E23="",NOT(ISNUMBER(G23))),"",E23-F23-G23)</f>
         <v/>
       </c>
       <c r="I23" s="26">
@@ -1600,23 +1600,23 @@
         <v/>
       </c>
       <c r="J23" s="26">
-        <f>IF(E23="","",H23-I23)</f>
+        <f>IF(OR(NOT(ISNUMBER(H23)),NOT(ISNUMBER(I23))),"",H23-I23)</f>
         <v/>
       </c>
       <c r="K23" s="33">
-        <f>IF(OR(E23="",B23=0),"",J23/B23)</f>
+        <f>IF(OR(NOT(ISNUMBER(J23)),N(B23)=0),"",J23/B23)</f>
         <v/>
       </c>
       <c r="L23" s="26">
-        <f>IF(OR(E23="",$B$12=0),"",H23/($B$12/60))</f>
+        <f>IF(OR(NOT(ISNUMBER(H23)),N($B$12)=0),"",H23/($B$12/60))</f>
         <v/>
       </c>
       <c r="M23" s="34">
-        <f>IF(L23="","",L23/$B$14-1)</f>
+        <f>IF(OR(L23="",NOT(ISNUMBER($B$14))),"",L23/$B$14-1)</f>
         <v/>
       </c>
       <c r="N23" s="30">
-        <f>IF(E23="","",IF(J23&lt;0,"Não cobre o custo cheio",IF(K23&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))</f>
+        <f>IF(E23="","",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I23)),"Falta o custo-hora em Config",IF(J23&lt;0,"Não cobre o custo cheio",IF(K23&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))))</f>
         <v/>
       </c>
     </row>
@@ -1643,11 +1643,11 @@
         <v/>
       </c>
       <c r="G24" s="26">
-        <f>IF(E24="","",E24*Config!$B$6)</f>
+        <f>IF(OR(E24="",NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E24*Config!$B$6)</f>
         <v/>
       </c>
       <c r="H24" s="28">
-        <f>IF(E24="","",E24-F24-G24)</f>
+        <f>IF(OR(E24="",NOT(ISNUMBER(G24))),"",E24-F24-G24)</f>
         <v/>
       </c>
       <c r="I24" s="26">
@@ -1655,23 +1655,23 @@
         <v/>
       </c>
       <c r="J24" s="26">
-        <f>IF(E24="","",H24-I24)</f>
+        <f>IF(OR(NOT(ISNUMBER(H24)),NOT(ISNUMBER(I24))),"",H24-I24)</f>
         <v/>
       </c>
       <c r="K24" s="33">
-        <f>IF(OR(E24="",B24=0),"",J24/B24)</f>
+        <f>IF(OR(NOT(ISNUMBER(J24)),N(B24)=0),"",J24/B24)</f>
         <v/>
       </c>
       <c r="L24" s="26">
-        <f>IF(OR(E24="",$B$12=0),"",H24/($B$12/60))</f>
+        <f>IF(OR(NOT(ISNUMBER(H24)),N($B$12)=0),"",H24/($B$12/60))</f>
         <v/>
       </c>
       <c r="M24" s="34">
-        <f>IF(L24="","",L24/$B$14-1)</f>
+        <f>IF(OR(L24="",NOT(ISNUMBER($B$14))),"",L24/$B$14-1)</f>
         <v/>
       </c>
       <c r="N24" s="30">
-        <f>IF(E24="","",IF(J24&lt;0,"Não cobre o custo cheio",IF(K24&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))</f>
+        <f>IF(E24="","",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I24)),"Falta o custo-hora em Config",IF(J24&lt;0,"Não cobre o custo cheio",IF(K24&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))))</f>
         <v/>
       </c>
     </row>
@@ -1997,11 +1997,11 @@
         <v>20968.4</v>
       </c>
       <c r="E43" s="38">
-        <f>IF(D43="","",B43*$B$13)</f>
+        <f>IF(OR(A43="",B43="",NOT(ISNUMBER($B$13))),"",B43*$B$13)</f>
         <v>8101.33333333333</v>
       </c>
       <c r="F43" s="38">
-        <f>IF(D43="","",D43-E43)</f>
+        <f>IF(OR(D43="",E43=""),"",D43-E43)</f>
         <v>12867.0666666667</v>
       </c>
       <c r="G43" s="33">
@@ -2030,11 +2030,11 @@
         <v>2546.25</v>
       </c>
       <c r="E44" s="38">
-        <f>IF(D44="","",B44*$B$13)</f>
+        <f>IF(OR(A44="",B44="",NOT(ISNUMBER($B$13))),"",B44*$B$13)</f>
         <v>3266.66666666667</v>
       </c>
       <c r="F44" s="38">
-        <f>IF(D44="","",D44-E44)</f>
+        <f>IF(OR(D44="",E44=""),"",D44-E44)</f>
         <v>-720.416666666667</v>
       </c>
       <c r="G44" s="33">
@@ -2063,11 +2063,11 @@
         <v>2446.35</v>
       </c>
       <c r="E45" s="38">
-        <f>IF(D45="","",B45*$B$13)</f>
+        <f>IF(OR(A45="",B45="",NOT(ISNUMBER($B$13))),"",B45*$B$13)</f>
         <v>3920</v>
       </c>
       <c r="F45" s="38">
-        <f>IF(D45="","",D45-E45)</f>
+        <f>IF(OR(D45="",E45=""),"",D45-E45)</f>
         <v>-1473.65</v>
       </c>
       <c r="G45" s="33">
@@ -2096,11 +2096,11 @@
         <v>905.58</v>
       </c>
       <c r="E46" s="38">
-        <f>IF(D46="","",B46*$B$13)</f>
+        <f>IF(OR(A46="",B46="",NOT(ISNUMBER($B$13))),"",B46*$B$13)</f>
         <v>1698.66666666667</v>
       </c>
       <c r="F46" s="38">
-        <f>IF(D46="","",D46-E46)</f>
+        <f>IF(OR(D46="",E46=""),"",D46-E46)</f>
         <v>-793.086666666667</v>
       </c>
       <c r="G46" s="33">
@@ -2127,11 +2127,11 @@
         <v/>
       </c>
       <c r="E47" s="38">
-        <f>IF(D47="","",B47*$B$13)</f>
+        <f>IF(OR(A47="",B47="",NOT(ISNUMBER($B$13))),"",B47*$B$13)</f>
         <v/>
       </c>
       <c r="F47" s="38">
-        <f>IF(D47="","",D47-E47)</f>
+        <f>IF(OR(D47="",E47=""),"",D47-E47)</f>
         <v/>
       </c>
       <c r="G47" s="33">
@@ -2158,11 +2158,11 @@
         <v/>
       </c>
       <c r="E48" s="38">
-        <f>IF(D48="","",B48*$B$13)</f>
+        <f>IF(OR(A48="",B48="",NOT(ISNUMBER($B$13))),"",B48*$B$13)</f>
         <v/>
       </c>
       <c r="F48" s="38">
-        <f>IF(D48="","",D48-E48)</f>
+        <f>IF(OR(D48="",E48=""),"",D48-E48)</f>
         <v/>
       </c>
       <c r="G48" s="33">
@@ -2189,15 +2189,15 @@
         <v>82.3333333333333</v>
       </c>
       <c r="D49" s="42">
-        <f>SUM(D43:D48)</f>
+        <f>IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"margens inválidas",SUM(D43:D48))</f>
         <v>26866.58</v>
       </c>
       <c r="E49" s="42">
-        <f>SUM(E43:E48)</f>
+        <f>IF(NOT(ISNUMBER($B$13)),"falta o custo-hora",SUM(E43:E48))</f>
         <v>16986.6666666667</v>
       </c>
       <c r="F49" s="42">
-        <f>SUM(F43:F48)</f>
+        <f>IF(OR(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),NOT(ISNUMBER($B$13))),IF(NOT(ISNUMBER($B$13)),"falta o custo-hora","margens inválidas"),SUM(F43:F48))</f>
         <v>9879.91333333333</v>
       </c>
     </row>
@@ -2711,9 +2711,15 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="3">
     <dataValidation sqref="C19:C30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e impostos + margem abaixo de 100 %." type="custom">
+      <formula1>=AND(ISNUMBER(B6),B6&gt;=0,B6&lt;1,B6+N(B7)&lt;1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem entre 0 % e 99 %, e impostos + margem abaixo de 100 %." type="custom">
+      <formula1>=AND(ISNUMBER(B7),B7&gt;=0,B7&lt;1,B7+N(B6)&lt;1)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
@@ -1386,7 +1386,7 @@
         <v>534</v>
       </c>
       <c r="M19" s="34">
-        <f>IF(OR(L19="",NOT(ISNUMBER($B$14))),"",L19/$B$14-1)</f>
+        <f>IF(OR(L19="",NOT(ISNUMBER($B$14))),"",IF($B$14=0,"sem base (mínimo zero)",L19/$B$14-1))</f>
         <v>0.5753</v>
       </c>
       <c r="N19" s="30" t="str">
@@ -1443,7 +1443,7 @@
         <v>160.815789473684</v>
       </c>
       <c r="M20" s="34">
-        <f>IF(OR(L20="",NOT(ISNUMBER($B$14))),"",L20/$B$14-1)</f>
+        <f>IF(OR(L20="",NOT(ISNUMBER($B$14))),"",IF($B$14=0,"sem base (mínimo zero)",L20/$B$14-1))</f>
         <v>-0.525593421052632</v>
       </c>
       <c r="N20" s="30" t="str">
@@ -1500,7 +1500,7 @@
         <v>128.755263157895</v>
       </c>
       <c r="M21" s="34">
-        <f>IF(OR(L21="",NOT(ISNUMBER($B$14))),"",L21/$B$14-1)</f>
+        <f>IF(OR(L21="",NOT(ISNUMBER($B$14))),"",IF($B$14=0,"sem base (mínimo zero)",L21/$B$14-1))</f>
         <v>-0.62017197368421</v>
       </c>
       <c r="N21" s="30" t="str">
@@ -1557,7 +1557,7 @@
         <v>109.989473684211</v>
       </c>
       <c r="M22" s="34">
-        <f>IF(OR(L22="",NOT(ISNUMBER($B$14))),"",L22/$B$14-1)</f>
+        <f>IF(OR(L22="",NOT(ISNUMBER($B$14))),"",IF($B$14=0,"sem base (mínimo zero)",L22/$B$14-1))</f>
         <v>-0.675531052631579</v>
       </c>
       <c r="N22" s="30" t="str">
@@ -1612,7 +1612,7 @@
         <v/>
       </c>
       <c r="M23" s="34">
-        <f>IF(OR(L23="",NOT(ISNUMBER($B$14))),"",L23/$B$14-1)</f>
+        <f>IF(OR(L23="",NOT(ISNUMBER($B$14))),"",IF($B$14=0,"sem base (mínimo zero)",L23/$B$14-1))</f>
         <v/>
       </c>
       <c r="N23" s="30">
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="M24" s="34">
-        <f>IF(OR(L24="",NOT(ISNUMBER($B$14))),"",L24/$B$14-1)</f>
+        <f>IF(OR(L24="",NOT(ISNUMBER($B$14))),"",IF($B$14=0,"sem base (mínimo zero)",L24/$B$14-1))</f>
         <v/>
       </c>
       <c r="N24" s="30">
@@ -2716,10 +2716,10 @@
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Impostos entre 0 % e 99 %, e impostos + margem abaixo de 100 %." type="custom">
-      <formula1>=AND(ISNUMBER(B6),B6&gt;=0,B6&lt;1,B6+N(B7)&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B6),AND(B6&gt;=0,B6&lt;1,B6+N(B7)&lt;1),FALSE)</formula1>
     </dataValidation>
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem entre 0 % e 99 %, e impostos + margem abaixo de 100 %." type="custom">
-      <formula1>=AND(ISNUMBER(B7),B7&gt;=0,B7&lt;1,B7+N(B6)&lt;1)</formula1>
+      <formula1>=IF(ISNUMBER(B7),AND(B7&gt;=0,B7&lt;1,B7+N(B6)&lt;1),FALSE)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B9" s="24">
-        <f>IFERROR(INDEX(Config!$B$19:$B$30,MATCH(B8,Config!$A$19:$A$30,0)),"")</f>
+        <f>IFERROR(IF(ISNUMBER(INDEX(Config!$B$19:$B$30,MATCH(B8,Config!$A$19:$A$30,0))),INDEX(Config!$B$19:$B$30,MATCH(B8,Config!$A$19:$A$30,0)),"faltam os minutos em Config"),"")</f>
         <v>30</v>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="B10" s="25" t="str">
-        <f>IFERROR(INDEX(Config!$C$19:$C$30,MATCH(B8,Config!$A$19:$A$30,0)),"")</f>
+        <f>IFERROR(IF(OR(INDEX(Config!$C$19:$C$30,MATCH(B8,Config!$A$19:$A$30,0))="Sim",INDEX(Config!$C$19:$C$30,MATCH(B8,Config!$A$19:$A$30,0))="Não"),INDEX(Config!$C$19:$C$30,MATCH(B8,Config!$A$19:$A$30,0)),"falta: gera retorno? em Config"),"")</f>
         <v>Sim</v>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B11" s="26">
-        <f>IFERROR(INDEX(Config!$D$19:$D$30,MATCH(B8,Config!$A$19:$A$30,0)),0)</f>
+        <f>IFERROR(IF(ISNUMBER(INDEX(Config!$D$19:$D$30,MATCH(B8,Config!$A$19:$A$30,0))),INDEX(Config!$D$19:$D$30,MATCH(B8,Config!$A$19:$A$30,0)),"falta o material em Config"),"")</f>
         <v>4</v>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B12" s="27">
-        <f>IF(B9="","",B9+IF(B10="Sim",Config!$E$19*Config!$F$19,0))</f>
+        <f>IF(B9="","",IF(NOT(IF(ISNUMBER(B9),AND(B9&gt;=0),FALSE)),"faltam os minutos",IF(AND(B10&lt;&gt;"Sim",B10&lt;&gt;"Não"),"falta: gera retorno?",IF(AND(B10="Sim",NOT(AND(IF(ISNUMBER(Config!$E$19),AND(Config!$E$19&gt;=0),FALSE),IF(ISNUMBER(Config!$F$19),AND(Config!$F$19&gt;=0),FALSE)))),"falta o retorno em Config",B9+IF(B10="Sim",Config!$E$19*Config!$F$19,0)))))</f>
         <v>38</v>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="B13" s="28">
-        <f>IF(B12="","",IF(NOT(ISNUMBER(Config!$B$5)),"falta o custo-hora em Config",B12/60*Config!$B$5+B11))</f>
+        <f>IF(B12="","",IF(NOT(ISNUMBER(B12)),B12,IF(NOT(ISNUMBER(Config!$B$5)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)),"falta o material",B12/60*Config!$B$5+B11))))</f>
         <v>130.666666666667</v>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -1346,27 +1346,27 @@
         <v>380</v>
       </c>
       <c r="C19" s="24">
-        <f>IF(Config!$A$10="","",Config!$B$10)</f>
+        <f>IF(Config!$A$10="","",IF(IF(ISNUMBER(Config!$B$10),AND(Config!$B$10&gt;=0),FALSE),Config!$B$10,"falta o prazo"))</f>
         <v>0</v>
       </c>
       <c r="D19" s="32">
-        <f>IF(Config!$A$10="","",Config!$C$10)</f>
+        <f>IF(Config!$A$10="","",IF(IF(ISNUMBER(Config!$C$10),AND(Config!$C$10&gt;=0,Config!$C$10&lt;=1),FALSE),Config!$C$10,"falta a glosa"))</f>
         <v>0</v>
       </c>
       <c r="E19" s="26">
-        <f>IF(OR(Config!$A$10="",B19=""),"",B19*(1-D19))</f>
+        <f>IF(OR(Config!$A$10="",B19=""),"",IF(NOT(IF(ISNUMBER(B19),AND(B19&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D19)),D19,B19*(1-D19))))</f>
         <v>380</v>
       </c>
       <c r="F19" s="26">
-        <f>IF(E19="","",E19*Config!$B$8*C19/30)</f>
+        <f>IF(OR(NOT(ISNUMBER(E19)),NOT(ISNUMBER(C19))),"",IF(C19=0,0,IF(NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE)),"",E19*Config!$B$8*C19/30)))</f>
         <v>0</v>
       </c>
       <c r="G19" s="26">
-        <f>IF(OR(E19="",NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E19*Config!$B$6)</f>
+        <f>IF(OR(NOT(ISNUMBER(E19)),NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E19*Config!$B$6)</f>
         <v>41.8</v>
       </c>
       <c r="H19" s="28">
-        <f>IF(OR(E19="",NOT(ISNUMBER(G19))),"",E19-F19-G19)</f>
+        <f>IF(OR(NOT(ISNUMBER(E19)),NOT(ISNUMBER(F19)),NOT(ISNUMBER(G19))),"",E19-F19-G19)</f>
         <v>338.2</v>
       </c>
       <c r="I19" s="26">
@@ -1390,7 +1390,7 @@
         <v>0.5753</v>
       </c>
       <c r="N19" s="30" t="str">
-        <f>IF(E19="","",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I19)),"Falta o custo-hora em Config",IF(J19&lt;0,"Não cobre o custo cheio",IF(K19&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))))</f>
+        <f>IF(E19="","",IF(NOT(ISNUMBER(E19)),E19,IF(NOT(ISNUMBER(C19)),C19,IF(AND(C19&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I19)),IF(ISNUMBER(Config!$B$5),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J19&lt;0,"Não cobre o custo cheio",IF(K19&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
         <v>Cobre custo e margem</v>
       </c>
     </row>
@@ -1403,27 +1403,27 @@
         <v>120</v>
       </c>
       <c r="C20" s="24">
-        <f>IF(Config!$A$11="","",Config!$B$11)</f>
+        <f>IF(Config!$A$11="","",IF(IF(ISNUMBER(Config!$B$11),AND(Config!$B$11&gt;=0),FALSE),Config!$B$11,"falta o prazo"))</f>
         <v>30</v>
       </c>
       <c r="D20" s="32">
-        <f>IF(Config!$A$11="","",Config!$C$11)</f>
+        <f>IF(Config!$A$11="","",IF(IF(ISNUMBER(Config!$C$11),AND(Config!$C$11&gt;=0,Config!$C$11&lt;=1),FALSE),Config!$C$11,"falta a glosa"))</f>
         <v>0.03</v>
       </c>
       <c r="E20" s="26">
-        <f>IF(OR(Config!$A$11="",B20=""),"",B20*(1-D20))</f>
+        <f>IF(OR(Config!$A$11="",B20=""),"",IF(NOT(IF(ISNUMBER(B20),AND(B20&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D20)),D20,B20*(1-D20))))</f>
         <v>116.4</v>
       </c>
       <c r="F20" s="26">
-        <f>IF(E20="","",E20*Config!$B$8*C20/30)</f>
+        <f>IF(OR(NOT(ISNUMBER(E20)),NOT(ISNUMBER(C20))),"",IF(C20=0,0,IF(NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE)),"",E20*Config!$B$8*C20/30)))</f>
         <v>1.746</v>
       </c>
       <c r="G20" s="26">
-        <f>IF(OR(E20="",NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E20*Config!$B$6)</f>
+        <f>IF(OR(NOT(ISNUMBER(E20)),NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E20*Config!$B$6)</f>
         <v>12.804</v>
       </c>
       <c r="H20" s="28">
-        <f>IF(OR(E20="",NOT(ISNUMBER(G20))),"",E20-F20-G20)</f>
+        <f>IF(OR(NOT(ISNUMBER(E20)),NOT(ISNUMBER(F20)),NOT(ISNUMBER(G20))),"",E20-F20-G20)</f>
         <v>101.85</v>
       </c>
       <c r="I20" s="26">
@@ -1447,7 +1447,7 @@
         <v>-0.525593421052632</v>
       </c>
       <c r="N20" s="30" t="str">
-        <f>IF(E20="","",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I20)),"Falta o custo-hora em Config",IF(J20&lt;0,"Não cobre o custo cheio",IF(K20&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))))</f>
+        <f>IF(E20="","",IF(NOT(ISNUMBER(E20)),E20,IF(NOT(ISNUMBER(C20)),C20,IF(AND(C20&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I20)),IF(ISNUMBER(Config!$B$5),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J20&lt;0,"Não cobre o custo cheio",IF(K20&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
         <v>Não cobre o custo cheio</v>
       </c>
     </row>
@@ -1460,27 +1460,27 @@
         <v>100</v>
       </c>
       <c r="C21" s="24">
-        <f>IF(Config!$A$12="","",Config!$B$12)</f>
+        <f>IF(Config!$A$12="","",IF(IF(ISNUMBER(Config!$B$12),AND(Config!$B$12&gt;=0),FALSE),Config!$B$12,"falta o prazo"))</f>
         <v>45</v>
       </c>
       <c r="D21" s="32">
-        <f>IF(Config!$A$12="","",Config!$C$12)</f>
+        <f>IF(Config!$A$12="","",IF(IF(ISNUMBER(Config!$C$12),AND(Config!$C$12&gt;=0,Config!$C$12&lt;=1),FALSE),Config!$C$12,"falta a glosa"))</f>
         <v>0.06</v>
       </c>
       <c r="E21" s="26">
-        <f>IF(OR(Config!$A$12="",B21=""),"",B21*(1-D21))</f>
+        <f>IF(OR(Config!$A$12="",B21=""),"",IF(NOT(IF(ISNUMBER(B21),AND(B21&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D21)),D21,B21*(1-D21))))</f>
         <v>94</v>
       </c>
       <c r="F21" s="26">
-        <f>IF(E21="","",E21*Config!$B$8*C21/30)</f>
+        <f>IF(OR(NOT(ISNUMBER(E21)),NOT(ISNUMBER(C21))),"",IF(C21=0,0,IF(NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE)),"",E21*Config!$B$8*C21/30)))</f>
         <v>2.115</v>
       </c>
       <c r="G21" s="26">
-        <f>IF(OR(E21="",NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E21*Config!$B$6)</f>
+        <f>IF(OR(NOT(ISNUMBER(E21)),NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E21*Config!$B$6)</f>
         <v>10.34</v>
       </c>
       <c r="H21" s="28">
-        <f>IF(OR(E21="",NOT(ISNUMBER(G21))),"",E21-F21-G21)</f>
+        <f>IF(OR(NOT(ISNUMBER(E21)),NOT(ISNUMBER(F21)),NOT(ISNUMBER(G21))),"",E21-F21-G21)</f>
         <v>81.545</v>
       </c>
       <c r="I21" s="26">
@@ -1504,7 +1504,7 @@
         <v>-0.62017197368421</v>
       </c>
       <c r="N21" s="30" t="str">
-        <f>IF(E21="","",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I21)),"Falta o custo-hora em Config",IF(J21&lt;0,"Não cobre o custo cheio",IF(K21&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))))</f>
+        <f>IF(E21="","",IF(NOT(ISNUMBER(E21)),E21,IF(NOT(ISNUMBER(C21)),C21,IF(AND(C21&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I21)),IF(ISNUMBER(Config!$B$5),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J21&lt;0,"Não cobre o custo cheio",IF(K21&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
         <v>Não cobre o custo cheio</v>
       </c>
     </row>
@@ -1517,27 +1517,27 @@
         <v>90</v>
       </c>
       <c r="C22" s="24">
-        <f>IF(Config!$A$13="","",Config!$B$13)</f>
+        <f>IF(Config!$A$13="","",IF(IF(ISNUMBER(Config!$B$13),AND(Config!$B$13&gt;=0),FALSE),Config!$B$13,"falta o prazo"))</f>
         <v>60</v>
       </c>
       <c r="D22" s="32">
-        <f>IF(Config!$A$13="","",Config!$C$13)</f>
+        <f>IF(Config!$A$13="","",IF(IF(ISNUMBER(Config!$C$13),AND(Config!$C$13&gt;=0,Config!$C$13&lt;=1),FALSE),Config!$C$13,"falta a glosa"))</f>
         <v>0.1</v>
       </c>
       <c r="E22" s="26">
-        <f>IF(OR(Config!$A$13="",B22=""),"",B22*(1-D22))</f>
+        <f>IF(OR(Config!$A$13="",B22=""),"",IF(NOT(IF(ISNUMBER(B22),AND(B22&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D22)),D22,B22*(1-D22))))</f>
         <v>81</v>
       </c>
       <c r="F22" s="26">
-        <f>IF(E22="","",E22*Config!$B$8*C22/30)</f>
+        <f>IF(OR(NOT(ISNUMBER(E22)),NOT(ISNUMBER(C22))),"",IF(C22=0,0,IF(NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE)),"",E22*Config!$B$8*C22/30)))</f>
         <v>2.43</v>
       </c>
       <c r="G22" s="26">
-        <f>IF(OR(E22="",NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E22*Config!$B$6)</f>
+        <f>IF(OR(NOT(ISNUMBER(E22)),NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E22*Config!$B$6)</f>
         <v>8.91</v>
       </c>
       <c r="H22" s="28">
-        <f>IF(OR(E22="",NOT(ISNUMBER(G22))),"",E22-F22-G22)</f>
+        <f>IF(OR(NOT(ISNUMBER(E22)),NOT(ISNUMBER(F22)),NOT(ISNUMBER(G22))),"",E22-F22-G22)</f>
         <v>69.66</v>
       </c>
       <c r="I22" s="26">
@@ -1561,7 +1561,7 @@
         <v>-0.675531052631579</v>
       </c>
       <c r="N22" s="30" t="str">
-        <f>IF(E22="","",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I22)),"Falta o custo-hora em Config",IF(J22&lt;0,"Não cobre o custo cheio",IF(K22&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))))</f>
+        <f>IF(E22="","",IF(NOT(ISNUMBER(E22)),E22,IF(NOT(ISNUMBER(C22)),C22,IF(AND(C22&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I22)),IF(ISNUMBER(Config!$B$5),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J22&lt;0,"Não cobre o custo cheio",IF(K22&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
         <v>Não cobre o custo cheio</v>
       </c>
     </row>
@@ -1572,27 +1572,27 @@
       </c>
       <c r="B23" s="31" t="n"/>
       <c r="C23" s="24">
-        <f>IF(Config!$A$14="","",Config!$B$14)</f>
+        <f>IF(Config!$A$14="","",IF(IF(ISNUMBER(Config!$B$14),AND(Config!$B$14&gt;=0),FALSE),Config!$B$14,"falta o prazo"))</f>
         <v/>
       </c>
       <c r="D23" s="32">
-        <f>IF(Config!$A$14="","",Config!$C$14)</f>
+        <f>IF(Config!$A$14="","",IF(IF(ISNUMBER(Config!$C$14),AND(Config!$C$14&gt;=0,Config!$C$14&lt;=1),FALSE),Config!$C$14,"falta a glosa"))</f>
         <v/>
       </c>
       <c r="E23" s="26">
-        <f>IF(OR(Config!$A$14="",B23=""),"",B23*(1-D23))</f>
+        <f>IF(OR(Config!$A$14="",B23=""),"",IF(NOT(IF(ISNUMBER(B23),AND(B23&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D23)),D23,B23*(1-D23))))</f>
         <v/>
       </c>
       <c r="F23" s="26">
-        <f>IF(E23="","",E23*Config!$B$8*C23/30)</f>
+        <f>IF(OR(NOT(ISNUMBER(E23)),NOT(ISNUMBER(C23))),"",IF(C23=0,0,IF(NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE)),"",E23*Config!$B$8*C23/30)))</f>
         <v/>
       </c>
       <c r="G23" s="26">
-        <f>IF(OR(E23="",NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E23*Config!$B$6)</f>
+        <f>IF(OR(NOT(ISNUMBER(E23)),NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E23*Config!$B$6)</f>
         <v/>
       </c>
       <c r="H23" s="28">
-        <f>IF(OR(E23="",NOT(ISNUMBER(G23))),"",E23-F23-G23)</f>
+        <f>IF(OR(NOT(ISNUMBER(E23)),NOT(ISNUMBER(F23)),NOT(ISNUMBER(G23))),"",E23-F23-G23)</f>
         <v/>
       </c>
       <c r="I23" s="26">
@@ -1616,7 +1616,7 @@
         <v/>
       </c>
       <c r="N23" s="30">
-        <f>IF(E23="","",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I23)),"Falta o custo-hora em Config",IF(J23&lt;0,"Não cobre o custo cheio",IF(K23&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))))</f>
+        <f>IF(E23="","",IF(NOT(ISNUMBER(E23)),E23,IF(NOT(ISNUMBER(C23)),C23,IF(AND(C23&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I23)),IF(ISNUMBER(Config!$B$5),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J23&lt;0,"Não cobre o custo cheio",IF(K23&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1627,27 +1627,27 @@
       </c>
       <c r="B24" s="31" t="n"/>
       <c r="C24" s="24">
-        <f>IF(Config!$A$15="","",Config!$B$15)</f>
+        <f>IF(Config!$A$15="","",IF(IF(ISNUMBER(Config!$B$15),AND(Config!$B$15&gt;=0),FALSE),Config!$B$15,"falta o prazo"))</f>
         <v/>
       </c>
       <c r="D24" s="32">
-        <f>IF(Config!$A$15="","",Config!$C$15)</f>
+        <f>IF(Config!$A$15="","",IF(IF(ISNUMBER(Config!$C$15),AND(Config!$C$15&gt;=0,Config!$C$15&lt;=1),FALSE),Config!$C$15,"falta a glosa"))</f>
         <v/>
       </c>
       <c r="E24" s="26">
-        <f>IF(OR(Config!$A$15="",B24=""),"",B24*(1-D24))</f>
+        <f>IF(OR(Config!$A$15="",B24=""),"",IF(NOT(IF(ISNUMBER(B24),AND(B24&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D24)),D24,B24*(1-D24))))</f>
         <v/>
       </c>
       <c r="F24" s="26">
-        <f>IF(E24="","",E24*Config!$B$8*C24/30)</f>
+        <f>IF(OR(NOT(ISNUMBER(E24)),NOT(ISNUMBER(C24))),"",IF(C24=0,0,IF(NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE)),"",E24*Config!$B$8*C24/30)))</f>
         <v/>
       </c>
       <c r="G24" s="26">
-        <f>IF(OR(E24="",NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E24*Config!$B$6)</f>
+        <f>IF(OR(NOT(ISNUMBER(E24)),NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE))),"",E24*Config!$B$6)</f>
         <v/>
       </c>
       <c r="H24" s="28">
-        <f>IF(OR(E24="",NOT(ISNUMBER(G24))),"",E24-F24-G24)</f>
+        <f>IF(OR(NOT(ISNUMBER(E24)),NOT(ISNUMBER(F24)),NOT(ISNUMBER(G24))),"",E24-F24-G24)</f>
         <v/>
       </c>
       <c r="I24" s="26">
@@ -1671,7 +1671,7 @@
         <v/>
       </c>
       <c r="N24" s="30">
-        <f>IF(E24="","",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I24)),"Falta o custo-hora em Config",IF(J24&lt;0,"Não cobre o custo cheio",IF(K24&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem")))))</f>
+        <f>IF(E24="","",IF(NOT(ISNUMBER(E24)),E24,IF(NOT(ISNUMBER(C24)),C24,IF(AND(C24&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I24)),IF(ISNUMBER(Config!$B$5),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J24&lt;0,"Não cobre o custo cheio",IF(K24&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         <v>4</v>
       </c>
       <c r="D31" s="28">
-        <f>IF(B31="","",B31-C31)</f>
+        <f>IF(OR(B31="",NOT(ISNUMBER(C31))),"",B31-C31)</f>
         <v>334.2</v>
       </c>
       <c r="E31" s="26">
-        <f>IF(OR(D31="",$B$12=0),"",D31/($B$12/60))</f>
+        <f>IF(OR(D31="",N($B$12)=0),"",D31/($B$12/60))</f>
         <v>527.684210526316</v>
       </c>
       <c r="F31" s="27">
@@ -1779,11 +1779,11 @@
         <v>4</v>
       </c>
       <c r="D32" s="28">
-        <f>IF(B32="","",B32-C32)</f>
+        <f>IF(OR(B32="",NOT(ISNUMBER(C32))),"",B32-C32)</f>
         <v>97.85</v>
       </c>
       <c r="E32" s="26">
-        <f>IF(OR(D32="",$B$12=0),"",D32/($B$12/60))</f>
+        <f>IF(OR(D32="",N($B$12)=0),"",D32/($B$12/60))</f>
         <v>154.5</v>
       </c>
       <c r="F32" s="27">
@@ -1809,11 +1809,11 @@
         <v>4</v>
       </c>
       <c r="D33" s="28">
-        <f>IF(B33="","",B33-C33)</f>
+        <f>IF(OR(B33="",NOT(ISNUMBER(C33))),"",B33-C33)</f>
         <v>77.545</v>
       </c>
       <c r="E33" s="26">
-        <f>IF(OR(D33="",$B$12=0),"",D33/($B$12/60))</f>
+        <f>IF(OR(D33="",N($B$12)=0),"",D33/($B$12/60))</f>
         <v>122.439473684211</v>
       </c>
       <c r="F33" s="27">
@@ -1839,11 +1839,11 @@
         <v>4</v>
       </c>
       <c r="D34" s="28">
-        <f>IF(B34="","",B34-C34)</f>
+        <f>IF(OR(B34="",NOT(ISNUMBER(C34))),"",B34-C34)</f>
         <v>65.66</v>
       </c>
       <c r="E34" s="26">
-        <f>IF(OR(D34="",$B$12=0),"",D34/($B$12/60))</f>
+        <f>IF(OR(D34="",N($B$12)=0),"",D34/($B$12/60))</f>
         <v>103.673684210526</v>
       </c>
       <c r="F34" s="27">
@@ -1869,11 +1869,11 @@
         <v/>
       </c>
       <c r="D35" s="28">
-        <f>IF(B35="","",B35-C35)</f>
+        <f>IF(OR(B35="",NOT(ISNUMBER(C35))),"",B35-C35)</f>
         <v/>
       </c>
       <c r="E35" s="26">
-        <f>IF(OR(D35="",$B$12=0),"",D35/($B$12/60))</f>
+        <f>IF(OR(D35="",N($B$12)=0),"",D35/($B$12/60))</f>
         <v/>
       </c>
       <c r="F35" s="27">
@@ -1899,11 +1899,11 @@
         <v/>
       </c>
       <c r="D36" s="28">
-        <f>IF(B36="","",B36-C36)</f>
+        <f>IF(OR(B36="",NOT(ISNUMBER(C36))),"",B36-C36)</f>
         <v/>
       </c>
       <c r="E36" s="26">
-        <f>IF(OR(D36="",$B$12=0),"",D36/($B$12/60))</f>
+        <f>IF(OR(D36="",N($B$12)=0),"",D36/($B$12/60))</f>
         <v/>
       </c>
       <c r="F36" s="27">
@@ -1989,27 +1989,27 @@
         <v>62</v>
       </c>
       <c r="C43" s="37">
-        <f>IF(OR(A43="",B43=""),"",B43*$B$12/60)</f>
+        <f>IF(OR(A43="",B43=""),"",IF(AND(ISNUMBER(B43),ISNUMBER($B$12)),B43*$B$12/60,""))</f>
         <v>39.2666666666667</v>
       </c>
       <c r="D43" s="38">
-        <f>IF(OR(A43="",B43="",H19=""),"",B43*H19)</f>
+        <f>IF(OR(A43="",B43=""),"",IF(NOT(IF(ISNUMBER(B43),AND(B43&gt;=0),FALSE)),"atendimentos inválidos",IF(B43=0,0,IF(NOT(ISNUMBER(H19)),"falta o valor líquido",B43*H19))))</f>
         <v>20968.4</v>
       </c>
       <c r="E43" s="38">
-        <f>IF(OR(A43="",B43="",NOT(ISNUMBER($B$13))),"",B43*$B$13)</f>
+        <f>IF(OR(A43="",B43="",NOT(IF(ISNUMBER(B43),AND(B43&gt;=0),FALSE)),NOT(ISNUMBER($B$13))),"",B43*$B$13)</f>
         <v>8101.33333333333</v>
       </c>
       <c r="F43" s="38">
-        <f>IF(OR(D43="",E43=""),"",D43-E43)</f>
+        <f>IF(AND(ISNUMBER(D43),ISNUMBER(E43)),D43-E43,"")</f>
         <v>12867.0666666667</v>
       </c>
       <c r="G43" s="33">
-        <f>IF(OR(D43="",$B$49=0),"",B43/$B$49)</f>
+        <f>IF(OR(NOT(ISNUMBER(B43)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B43/$B$49)</f>
         <v>0.476923076923077</v>
       </c>
       <c r="H43" s="33">
-        <f>IF(OR(D43="",$D$49=0),"",D43/$D$49)</f>
+        <f>IF(OR(NOT(ISNUMBER(D43)),NOT(ISNUMBER($D$49)),N($D$49)=0),"",D43/$D$49)</f>
         <v>0.780464056087526</v>
       </c>
     </row>
@@ -2022,27 +2022,27 @@
         <v>25</v>
       </c>
       <c r="C44" s="37">
-        <f>IF(OR(A44="",B44=""),"",B44*$B$12/60)</f>
+        <f>IF(OR(A44="",B44=""),"",IF(AND(ISNUMBER(B44),ISNUMBER($B$12)),B44*$B$12/60,""))</f>
         <v>15.8333333333333</v>
       </c>
       <c r="D44" s="38">
-        <f>IF(OR(A44="",B44="",H20=""),"",B44*H20)</f>
+        <f>IF(OR(A44="",B44=""),"",IF(NOT(IF(ISNUMBER(B44),AND(B44&gt;=0),FALSE)),"atendimentos inválidos",IF(B44=0,0,IF(NOT(ISNUMBER(H20)),"falta o valor líquido",B44*H20))))</f>
         <v>2546.25</v>
       </c>
       <c r="E44" s="38">
-        <f>IF(OR(A44="",B44="",NOT(ISNUMBER($B$13))),"",B44*$B$13)</f>
+        <f>IF(OR(A44="",B44="",NOT(IF(ISNUMBER(B44),AND(B44&gt;=0),FALSE)),NOT(ISNUMBER($B$13))),"",B44*$B$13)</f>
         <v>3266.66666666667</v>
       </c>
       <c r="F44" s="38">
-        <f>IF(OR(D44="",E44=""),"",D44-E44)</f>
+        <f>IF(AND(ISNUMBER(D44),ISNUMBER(E44)),D44-E44,"")</f>
         <v>-720.416666666667</v>
       </c>
       <c r="G44" s="33">
-        <f>IF(OR(D44="",$B$49=0),"",B44/$B$49)</f>
+        <f>IF(OR(NOT(ISNUMBER(B44)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B44/$B$49)</f>
         <v>0.192307692307692</v>
       </c>
       <c r="H44" s="33">
-        <f>IF(OR(D44="",$D$49=0),"",D44/$D$49)</f>
+        <f>IF(OR(NOT(ISNUMBER(D44)),NOT(ISNUMBER($D$49)),N($D$49)=0),"",D44/$D$49)</f>
         <v>0.0947738789231827</v>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
         <v>30</v>
       </c>
       <c r="C45" s="37">
-        <f>IF(OR(A45="",B45=""),"",B45*$B$12/60)</f>
+        <f>IF(OR(A45="",B45=""),"",IF(AND(ISNUMBER(B45),ISNUMBER($B$12)),B45*$B$12/60,""))</f>
         <v>19</v>
       </c>
       <c r="D45" s="38">
-        <f>IF(OR(A45="",B45="",H21=""),"",B45*H21)</f>
+        <f>IF(OR(A45="",B45=""),"",IF(NOT(IF(ISNUMBER(B45),AND(B45&gt;=0),FALSE)),"atendimentos inválidos",IF(B45=0,0,IF(NOT(ISNUMBER(H21)),"falta o valor líquido",B45*H21))))</f>
         <v>2446.35</v>
       </c>
       <c r="E45" s="38">
-        <f>IF(OR(A45="",B45="",NOT(ISNUMBER($B$13))),"",B45*$B$13)</f>
+        <f>IF(OR(A45="",B45="",NOT(IF(ISNUMBER(B45),AND(B45&gt;=0),FALSE)),NOT(ISNUMBER($B$13))),"",B45*$B$13)</f>
         <v>3920</v>
       </c>
       <c r="F45" s="38">
-        <f>IF(OR(D45="",E45=""),"",D45-E45)</f>
+        <f>IF(AND(ISNUMBER(D45),ISNUMBER(E45)),D45-E45,"")</f>
         <v>-1473.65</v>
       </c>
       <c r="G45" s="33">
-        <f>IF(OR(D45="",$B$49=0),"",B45/$B$49)</f>
+        <f>IF(OR(NOT(ISNUMBER(B45)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B45/$B$49)</f>
         <v>0.230769230769231</v>
       </c>
       <c r="H45" s="33">
-        <f>IF(OR(D45="",$D$49=0),"",D45/$D$49)</f>
+        <f>IF(OR(NOT(ISNUMBER(D45)),NOT(ISNUMBER($D$49)),N($D$49)=0),"",D45/$D$49)</f>
         <v>0.0910555046455485</v>
       </c>
     </row>
@@ -2088,27 +2088,27 @@
         <v>13</v>
       </c>
       <c r="C46" s="37">
-        <f>IF(OR(A46="",B46=""),"",B46*$B$12/60)</f>
+        <f>IF(OR(A46="",B46=""),"",IF(AND(ISNUMBER(B46),ISNUMBER($B$12)),B46*$B$12/60,""))</f>
         <v>8.23333333333333</v>
       </c>
       <c r="D46" s="38">
-        <f>IF(OR(A46="",B46="",H22=""),"",B46*H22)</f>
+        <f>IF(OR(A46="",B46=""),"",IF(NOT(IF(ISNUMBER(B46),AND(B46&gt;=0),FALSE)),"atendimentos inválidos",IF(B46=0,0,IF(NOT(ISNUMBER(H22)),"falta o valor líquido",B46*H22))))</f>
         <v>905.58</v>
       </c>
       <c r="E46" s="38">
-        <f>IF(OR(A46="",B46="",NOT(ISNUMBER($B$13))),"",B46*$B$13)</f>
+        <f>IF(OR(A46="",B46="",NOT(IF(ISNUMBER(B46),AND(B46&gt;=0),FALSE)),NOT(ISNUMBER($B$13))),"",B46*$B$13)</f>
         <v>1698.66666666667</v>
       </c>
       <c r="F46" s="38">
-        <f>IF(OR(D46="",E46=""),"",D46-E46)</f>
+        <f>IF(AND(ISNUMBER(D46),ISNUMBER(E46)),D46-E46,"")</f>
         <v>-793.086666666667</v>
       </c>
       <c r="G46" s="33">
-        <f>IF(OR(D46="",$B$49=0),"",B46/$B$49)</f>
+        <f>IF(OR(NOT(ISNUMBER(B46)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B46/$B$49)</f>
         <v>0.1</v>
       </c>
       <c r="H46" s="33">
-        <f>IF(OR(D46="",$D$49=0),"",D46/$D$49)</f>
+        <f>IF(OR(NOT(ISNUMBER(D46)),NOT(ISNUMBER($D$49)),N($D$49)=0),"",D46/$D$49)</f>
         <v>0.0337065603437431</v>
       </c>
     </row>
@@ -2119,27 +2119,27 @@
       </c>
       <c r="B47" s="36" t="n"/>
       <c r="C47" s="37">
-        <f>IF(OR(A47="",B47=""),"",B47*$B$12/60)</f>
+        <f>IF(OR(A47="",B47=""),"",IF(AND(ISNUMBER(B47),ISNUMBER($B$12)),B47*$B$12/60,""))</f>
         <v/>
       </c>
       <c r="D47" s="38">
-        <f>IF(OR(A47="",B47="",H23=""),"",B47*H23)</f>
+        <f>IF(OR(A47="",B47=""),"",IF(NOT(IF(ISNUMBER(B47),AND(B47&gt;=0),FALSE)),"atendimentos inválidos",IF(B47=0,0,IF(NOT(ISNUMBER(H23)),"falta o valor líquido",B47*H23))))</f>
         <v/>
       </c>
       <c r="E47" s="38">
-        <f>IF(OR(A47="",B47="",NOT(ISNUMBER($B$13))),"",B47*$B$13)</f>
+        <f>IF(OR(A47="",B47="",NOT(IF(ISNUMBER(B47),AND(B47&gt;=0),FALSE)),NOT(ISNUMBER($B$13))),"",B47*$B$13)</f>
         <v/>
       </c>
       <c r="F47" s="38">
-        <f>IF(OR(D47="",E47=""),"",D47-E47)</f>
+        <f>IF(AND(ISNUMBER(D47),ISNUMBER(E47)),D47-E47,"")</f>
         <v/>
       </c>
       <c r="G47" s="33">
-        <f>IF(OR(D47="",$B$49=0),"",B47/$B$49)</f>
+        <f>IF(OR(NOT(ISNUMBER(B47)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B47/$B$49)</f>
         <v/>
       </c>
       <c r="H47" s="33">
-        <f>IF(OR(D47="",$D$49=0),"",D47/$D$49)</f>
+        <f>IF(OR(NOT(ISNUMBER(D47)),NOT(ISNUMBER($D$49)),N($D$49)=0),"",D47/$D$49)</f>
         <v/>
       </c>
     </row>
@@ -2150,27 +2150,27 @@
       </c>
       <c r="B48" s="36" t="n"/>
       <c r="C48" s="37">
-        <f>IF(OR(A48="",B48=""),"",B48*$B$12/60)</f>
+        <f>IF(OR(A48="",B48=""),"",IF(AND(ISNUMBER(B48),ISNUMBER($B$12)),B48*$B$12/60,""))</f>
         <v/>
       </c>
       <c r="D48" s="38">
-        <f>IF(OR(A48="",B48="",H24=""),"",B48*H24)</f>
+        <f>IF(OR(A48="",B48=""),"",IF(NOT(IF(ISNUMBER(B48),AND(B48&gt;=0),FALSE)),"atendimentos inválidos",IF(B48=0,0,IF(NOT(ISNUMBER(H24)),"falta o valor líquido",B48*H24))))</f>
         <v/>
       </c>
       <c r="E48" s="38">
-        <f>IF(OR(A48="",B48="",NOT(ISNUMBER($B$13))),"",B48*$B$13)</f>
+        <f>IF(OR(A48="",B48="",NOT(IF(ISNUMBER(B48),AND(B48&gt;=0),FALSE)),NOT(ISNUMBER($B$13))),"",B48*$B$13)</f>
         <v/>
       </c>
       <c r="F48" s="38">
-        <f>IF(OR(D48="",E48=""),"",D48-E48)</f>
+        <f>IF(AND(ISNUMBER(D48),ISNUMBER(E48)),D48-E48,"")</f>
         <v/>
       </c>
       <c r="G48" s="33">
-        <f>IF(OR(D48="",$B$49=0),"",B48/$B$49)</f>
+        <f>IF(OR(NOT(ISNUMBER(B48)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B48/$B$49)</f>
         <v/>
       </c>
       <c r="H48" s="33">
-        <f>IF(OR(D48="",$D$49=0),"",D48/$D$49)</f>
+        <f>IF(OR(NOT(ISNUMBER(D48)),NOT(ISNUMBER($D$49)),N($D$49)=0),"",D48/$D$49)</f>
         <v/>
       </c>
     </row>
@@ -2181,23 +2181,23 @@
         </is>
       </c>
       <c r="B49" s="40">
-        <f>SUM(B43:B48)</f>
+        <f>IF(SUMPRODUCT(ISTEXT(B43:B48)*1)&gt;0,"atendimentos com texto",SUM(B43:B48))</f>
         <v>130</v>
       </c>
       <c r="C49" s="41">
-        <f>SUM(C43:C48)</f>
+        <f>IF(OR(NOT(ISNUMBER(B49)),NOT(ISNUMBER($B$12))),"",SUM(C43:C48))</f>
         <v>82.3333333333333</v>
       </c>
       <c r="D49" s="42">
-        <f>IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"margens inválidas",SUM(D43:D48))</f>
+        <f>IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"margens inválidas",IF(SUMPRODUCT((B43:B48&lt;&gt;"")*(ISNUMBER(D43:D48)=FALSE))&gt;0,"líquido incompleto em "&amp;SUMPRODUCT((B43:B48&lt;&gt;"")*(ISNUMBER(D43:D48)=FALSE))&amp;" pagador(es)",SUM(D43:D48)))</f>
         <v>26866.58</v>
       </c>
       <c r="E49" s="42">
-        <f>IF(NOT(ISNUMBER($B$13)),"falta o custo-hora",SUM(E43:E48))</f>
+        <f>IF(NOT(ISNUMBER($B$13)),IF(ISNUMBER(Config!$B$5),"faltam dados do procedimento","falta o custo-hora"),IF(SUMPRODUCT(ISTEXT(B43:B48)*1)&gt;0,"atendimentos com texto",SUM(E43:E48)))</f>
         <v>16986.6666666667</v>
       </c>
       <c r="F49" s="42">
-        <f>IF(OR(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),NOT(ISNUMBER($B$13))),IF(NOT(ISNUMBER($B$13)),"falta o custo-hora","margens inválidas"),SUM(F43:F48))</f>
+        <f>IF(NOT(ISNUMBER(D49)),D49,IF(NOT(ISNUMBER(E49)),E49,SUM(F43:F48)))</f>
         <v>9879.91333333333</v>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
   </mergeCells>
   <conditionalFormatting sqref="N19:N24">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>N19="Não cobre o custo cheio"</formula>
+      <formula>AND(N19&lt;&gt;"",N19&lt;&gt;"Cobre o custo, não a margem mínima",N19&lt;&gt;"Cobre custo e margem")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>N19="Cobre o custo, não a margem mínima"</formula>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
@@ -1133,13 +1133,13 @@
       </c>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="17" t="str">
-        <f>IFERROR(INDEX($A$20:$A$24,MATCH(MAX($L$20:$L$24),$L$20:$L$24,0))&amp;": R$ "&amp;FIXED(MAX($L$20:$L$24),0),"")</f>
+        <f>IF(SUMPRODUCT(($A$20:$A$24&lt;&gt;"")*($B$20:$B$24&lt;&gt;"")*(ISNUMBER($L$20:$L$24)=FALSE))&gt;0,"incompleto: "&amp;SUMPRODUCT(($A$20:$A$24&lt;&gt;"")*($B$20:$B$24&lt;&gt;"")*(ISNUMBER($L$20:$L$24)=FALSE))&amp;" convênio(s) sem líquido",IFERROR(INDEX($A$20:$A$24,MATCH(MAX($L$20:$L$24),$L$20:$L$24,0))&amp;": R$ "&amp;FIXED(MAX($L$20:$L$24),0),""))</f>
         <v>Saúde Total: R$ 161</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="18" t="str">
-        <f>IFERROR(INDEX($A$20:$A$24,MATCH(MIN($L$20:$L$24),$L$20:$L$24,0))&amp;": R$ "&amp;FIXED(MIN($L$20:$L$24),0),"")</f>
+        <f>IF(SUMPRODUCT(($A$20:$A$24&lt;&gt;"")*($B$20:$B$24&lt;&gt;"")*(ISNUMBER($L$20:$L$24)=FALSE))&gt;0,"incompleto: "&amp;SUMPRODUCT(($A$20:$A$24&lt;&gt;"")*($B$20:$B$24&lt;&gt;"")*(ISNUMBER($L$20:$L$24)=FALSE))&amp;" convênio(s) sem líquido",IFERROR(INDEX($A$20:$A$24,MATCH(MIN($L$20:$L$24),$L$20:$L$24,0))&amp;": R$ "&amp;FIXED(MIN($L$20:$L$24),0),""))</f>
         <v>Vida Care: R$ 110</v>
       </c>
       <c r="K5" s="14" t="n"/>
@@ -1989,11 +1989,11 @@
         <v>62</v>
       </c>
       <c r="C43" s="37">
-        <f>IF(OR(A43="",B43=""),"",IF(AND(ISNUMBER(B43),ISNUMBER($B$12)),B43*$B$12/60,""))</f>
+        <f>IF(OR(A43="",B43=""),"",IF(AND(IF(ISNUMBER(B43),AND(B43&gt;=0),FALSE),ISNUMBER($B$12)),B43*$B$12/60,""))</f>
         <v>39.2666666666667</v>
       </c>
       <c r="D43" s="38">
-        <f>IF(OR(A43="",B43=""),"",IF(NOT(IF(ISNUMBER(B43),AND(B43&gt;=0),FALSE)),"atendimentos inválidos",IF(B43=0,0,IF(NOT(ISNUMBER(H19)),"falta o valor líquido",B43*H19))))</f>
+        <f>IF(AND(A43="",B43=""),"",IF(B43="","",IF(A43="","pagador sem nome",IF(NOT(IF(ISNUMBER(B43),AND(B43&gt;=0),FALSE)),"atendimentos inválidos",IF(B43=0,0,IF(NOT(ISNUMBER(H19)),"falta o valor líquido",B43*H19))))))</f>
         <v>20968.4</v>
       </c>
       <c r="E43" s="38">
@@ -2005,7 +2005,7 @@
         <v>12867.0666666667</v>
       </c>
       <c r="G43" s="33">
-        <f>IF(OR(NOT(ISNUMBER(B43)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B43/$B$49)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(B43),AND(B43&gt;=0),FALSE)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B43/$B$49)</f>
         <v>0.476923076923077</v>
       </c>
       <c r="H43" s="33">
@@ -2022,11 +2022,11 @@
         <v>25</v>
       </c>
       <c r="C44" s="37">
-        <f>IF(OR(A44="",B44=""),"",IF(AND(ISNUMBER(B44),ISNUMBER($B$12)),B44*$B$12/60,""))</f>
+        <f>IF(OR(A44="",B44=""),"",IF(AND(IF(ISNUMBER(B44),AND(B44&gt;=0),FALSE),ISNUMBER($B$12)),B44*$B$12/60,""))</f>
         <v>15.8333333333333</v>
       </c>
       <c r="D44" s="38">
-        <f>IF(OR(A44="",B44=""),"",IF(NOT(IF(ISNUMBER(B44),AND(B44&gt;=0),FALSE)),"atendimentos inválidos",IF(B44=0,0,IF(NOT(ISNUMBER(H20)),"falta o valor líquido",B44*H20))))</f>
+        <f>IF(AND(A44="",B44=""),"",IF(B44="","",IF(A44="","pagador sem nome",IF(NOT(IF(ISNUMBER(B44),AND(B44&gt;=0),FALSE)),"atendimentos inválidos",IF(B44=0,0,IF(NOT(ISNUMBER(H20)),"falta o valor líquido",B44*H20))))))</f>
         <v>2546.25</v>
       </c>
       <c r="E44" s="38">
@@ -2038,7 +2038,7 @@
         <v>-720.416666666667</v>
       </c>
       <c r="G44" s="33">
-        <f>IF(OR(NOT(ISNUMBER(B44)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B44/$B$49)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(B44),AND(B44&gt;=0),FALSE)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B44/$B$49)</f>
         <v>0.192307692307692</v>
       </c>
       <c r="H44" s="33">
@@ -2055,11 +2055,11 @@
         <v>30</v>
       </c>
       <c r="C45" s="37">
-        <f>IF(OR(A45="",B45=""),"",IF(AND(ISNUMBER(B45),ISNUMBER($B$12)),B45*$B$12/60,""))</f>
+        <f>IF(OR(A45="",B45=""),"",IF(AND(IF(ISNUMBER(B45),AND(B45&gt;=0),FALSE),ISNUMBER($B$12)),B45*$B$12/60,""))</f>
         <v>19</v>
       </c>
       <c r="D45" s="38">
-        <f>IF(OR(A45="",B45=""),"",IF(NOT(IF(ISNUMBER(B45),AND(B45&gt;=0),FALSE)),"atendimentos inválidos",IF(B45=0,0,IF(NOT(ISNUMBER(H21)),"falta o valor líquido",B45*H21))))</f>
+        <f>IF(AND(A45="",B45=""),"",IF(B45="","",IF(A45="","pagador sem nome",IF(NOT(IF(ISNUMBER(B45),AND(B45&gt;=0),FALSE)),"atendimentos inválidos",IF(B45=0,0,IF(NOT(ISNUMBER(H21)),"falta o valor líquido",B45*H21))))))</f>
         <v>2446.35</v>
       </c>
       <c r="E45" s="38">
@@ -2071,7 +2071,7 @@
         <v>-1473.65</v>
       </c>
       <c r="G45" s="33">
-        <f>IF(OR(NOT(ISNUMBER(B45)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B45/$B$49)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(B45),AND(B45&gt;=0),FALSE)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B45/$B$49)</f>
         <v>0.230769230769231</v>
       </c>
       <c r="H45" s="33">
@@ -2088,11 +2088,11 @@
         <v>13</v>
       </c>
       <c r="C46" s="37">
-        <f>IF(OR(A46="",B46=""),"",IF(AND(ISNUMBER(B46),ISNUMBER($B$12)),B46*$B$12/60,""))</f>
+        <f>IF(OR(A46="",B46=""),"",IF(AND(IF(ISNUMBER(B46),AND(B46&gt;=0),FALSE),ISNUMBER($B$12)),B46*$B$12/60,""))</f>
         <v>8.23333333333333</v>
       </c>
       <c r="D46" s="38">
-        <f>IF(OR(A46="",B46=""),"",IF(NOT(IF(ISNUMBER(B46),AND(B46&gt;=0),FALSE)),"atendimentos inválidos",IF(B46=0,0,IF(NOT(ISNUMBER(H22)),"falta o valor líquido",B46*H22))))</f>
+        <f>IF(AND(A46="",B46=""),"",IF(B46="","",IF(A46="","pagador sem nome",IF(NOT(IF(ISNUMBER(B46),AND(B46&gt;=0),FALSE)),"atendimentos inválidos",IF(B46=0,0,IF(NOT(ISNUMBER(H22)),"falta o valor líquido",B46*H22))))))</f>
         <v>905.58</v>
       </c>
       <c r="E46" s="38">
@@ -2104,7 +2104,7 @@
         <v>-793.086666666667</v>
       </c>
       <c r="G46" s="33">
-        <f>IF(OR(NOT(ISNUMBER(B46)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B46/$B$49)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(B46),AND(B46&gt;=0),FALSE)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B46/$B$49)</f>
         <v>0.1</v>
       </c>
       <c r="H46" s="33">
@@ -2119,11 +2119,11 @@
       </c>
       <c r="B47" s="36" t="n"/>
       <c r="C47" s="37">
-        <f>IF(OR(A47="",B47=""),"",IF(AND(ISNUMBER(B47),ISNUMBER($B$12)),B47*$B$12/60,""))</f>
+        <f>IF(OR(A47="",B47=""),"",IF(AND(IF(ISNUMBER(B47),AND(B47&gt;=0),FALSE),ISNUMBER($B$12)),B47*$B$12/60,""))</f>
         <v/>
       </c>
       <c r="D47" s="38">
-        <f>IF(OR(A47="",B47=""),"",IF(NOT(IF(ISNUMBER(B47),AND(B47&gt;=0),FALSE)),"atendimentos inválidos",IF(B47=0,0,IF(NOT(ISNUMBER(H23)),"falta o valor líquido",B47*H23))))</f>
+        <f>IF(AND(A47="",B47=""),"",IF(B47="","",IF(A47="","pagador sem nome",IF(NOT(IF(ISNUMBER(B47),AND(B47&gt;=0),FALSE)),"atendimentos inválidos",IF(B47=0,0,IF(NOT(ISNUMBER(H23)),"falta o valor líquido",B47*H23))))))</f>
         <v/>
       </c>
       <c r="E47" s="38">
@@ -2135,7 +2135,7 @@
         <v/>
       </c>
       <c r="G47" s="33">
-        <f>IF(OR(NOT(ISNUMBER(B47)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B47/$B$49)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(B47),AND(B47&gt;=0),FALSE)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B47/$B$49)</f>
         <v/>
       </c>
       <c r="H47" s="33">
@@ -2150,11 +2150,11 @@
       </c>
       <c r="B48" s="36" t="n"/>
       <c r="C48" s="37">
-        <f>IF(OR(A48="",B48=""),"",IF(AND(ISNUMBER(B48),ISNUMBER($B$12)),B48*$B$12/60,""))</f>
+        <f>IF(OR(A48="",B48=""),"",IF(AND(IF(ISNUMBER(B48),AND(B48&gt;=0),FALSE),ISNUMBER($B$12)),B48*$B$12/60,""))</f>
         <v/>
       </c>
       <c r="D48" s="38">
-        <f>IF(OR(A48="",B48=""),"",IF(NOT(IF(ISNUMBER(B48),AND(B48&gt;=0),FALSE)),"atendimentos inválidos",IF(B48=0,0,IF(NOT(ISNUMBER(H24)),"falta o valor líquido",B48*H24))))</f>
+        <f>IF(AND(A48="",B48=""),"",IF(B48="","",IF(A48="","pagador sem nome",IF(NOT(IF(ISNUMBER(B48),AND(B48&gt;=0),FALSE)),"atendimentos inválidos",IF(B48=0,0,IF(NOT(ISNUMBER(H24)),"falta o valor líquido",B48*H24))))))</f>
         <v/>
       </c>
       <c r="E48" s="38">
@@ -2166,7 +2166,7 @@
         <v/>
       </c>
       <c r="G48" s="33">
-        <f>IF(OR(NOT(ISNUMBER(B48)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B48/$B$49)</f>
+        <f>IF(OR(NOT(IF(ISNUMBER(B48),AND(B48&gt;=0),FALSE)),NOT(ISNUMBER($B$49)),N($B$49)=0),"",B48/$B$49)</f>
         <v/>
       </c>
       <c r="H48" s="33">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="B49" s="40">
-        <f>IF(SUMPRODUCT(ISTEXT(B43:B48)*1)&gt;0,"atendimentos com texto",SUM(B43:B48))</f>
+        <f>IF(SUMPRODUCT((B43:B48&lt;&gt;"")*((A43:A48="")+ISTEXT(B43:B48)+ISNUMBER(B43:B48)*(B43:B48&lt;0)&gt;0))&gt;0,"atendimentos inválidos ou sem pagador",SUM(B43:B48))</f>
         <v>130</v>
       </c>
       <c r="C49" s="41">
@@ -2193,7 +2193,7 @@
         <v>26866.58</v>
       </c>
       <c r="E49" s="42">
-        <f>IF(NOT(ISNUMBER($B$13)),IF(ISNUMBER(Config!$B$5),"faltam dados do procedimento","falta o custo-hora"),IF(SUMPRODUCT(ISTEXT(B43:B48)*1)&gt;0,"atendimentos com texto",SUM(E43:E48)))</f>
+        <f>IF(NOT(ISNUMBER($B$13)),IF(ISNUMBER(Config!$B$5),"faltam dados do procedimento","falta o custo-hora"),IF(SUMPRODUCT((B43:B48&lt;&gt;"")*((A43:A48="")+ISTEXT(B43:B48)+ISNUMBER(B43:B48)*(B43:B48&lt;0)&gt;0))&gt;0,"atendimentos inválidos ou sem pagador",SUM(E43:E48)))</f>
         <v>16986.6666666667</v>
       </c>
       <c r="F49" s="42">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/07-simulador-convenio-x-particular.xlsx
@@ -1133,13 +1133,13 @@
       </c>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="17" t="str">
-        <f>IF(SUMPRODUCT(($A$20:$A$24&lt;&gt;"")*($B$20:$B$24&lt;&gt;"")*(ISNUMBER($L$20:$L$24)=FALSE))&gt;0,"incompleto: "&amp;SUMPRODUCT(($A$20:$A$24&lt;&gt;"")*($B$20:$B$24&lt;&gt;"")*(ISNUMBER($L$20:$L$24)=FALSE))&amp;" convênio(s) sem líquido",IFERROR(INDEX($A$20:$A$24,MATCH(MAX($L$20:$L$24),$L$20:$L$24,0))&amp;": R$ "&amp;FIXED(MAX($L$20:$L$24),0),""))</f>
+        <f>IF(SUMPRODUCT(($B$20:$B$24&lt;&gt;"")*(ISNUMBER($L$20:$L$24)=FALSE))&gt;0,"incompleto: "&amp;SUMPRODUCT(($B$20:$B$24&lt;&gt;"")*(ISNUMBER($L$20:$L$24)=FALSE))&amp;" convênio(s) sem líquido",IFERROR(INDEX($A$20:$A$24,MATCH(MAX($L$20:$L$24),$L$20:$L$24,0))&amp;": R$ "&amp;FIXED(MAX($L$20:$L$24),0),""))</f>
         <v>Saúde Total: R$ 161</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="18" t="str">
-        <f>IF(SUMPRODUCT(($A$20:$A$24&lt;&gt;"")*($B$20:$B$24&lt;&gt;"")*(ISNUMBER($L$20:$L$24)=FALSE))&gt;0,"incompleto: "&amp;SUMPRODUCT(($A$20:$A$24&lt;&gt;"")*($B$20:$B$24&lt;&gt;"")*(ISNUMBER($L$20:$L$24)=FALSE))&amp;" convênio(s) sem líquido",IFERROR(INDEX($A$20:$A$24,MATCH(MIN($L$20:$L$24),$L$20:$L$24,0))&amp;": R$ "&amp;FIXED(MIN($L$20:$L$24),0),""))</f>
+        <f>IF(SUMPRODUCT(($B$20:$B$24&lt;&gt;"")*(ISNUMBER($L$20:$L$24)=FALSE))&gt;0,"incompleto: "&amp;SUMPRODUCT(($B$20:$B$24&lt;&gt;"")*(ISNUMBER($L$20:$L$24)=FALSE))&amp;" convênio(s) sem líquido",IFERROR(INDEX($A$20:$A$24,MATCH(MIN($L$20:$L$24),$L$20:$L$24,0))&amp;": R$ "&amp;FIXED(MIN($L$20:$L$24),0),""))</f>
         <v>Vida Care: R$ 110</v>
       </c>
       <c r="K5" s="14" t="n"/>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B9" s="24">
-        <f>IFERROR(IF(ISNUMBER(INDEX(Config!$B$19:$B$30,MATCH(B8,Config!$A$19:$A$30,0))),INDEX(Config!$B$19:$B$30,MATCH(B8,Config!$A$19:$A$30,0)),"faltam os minutos em Config"),"")</f>
+        <f>IFERROR(IF(IF(ISNUMBER(INDEX(Config!$B$19:$B$30,MATCH(B8,Config!$A$19:$A$30,0))),AND(INDEX(Config!$B$19:$B$30,MATCH(B8,Config!$A$19:$A$30,0))&gt;=0),FALSE),INDEX(Config!$B$19:$B$30,MATCH(B8,Config!$A$19:$A$30,0)),"faltam os minutos em Config (número ≥ 0)"),"")</f>
         <v>30</v>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B11" s="26">
-        <f>IFERROR(IF(ISNUMBER(INDEX(Config!$D$19:$D$30,MATCH(B8,Config!$A$19:$A$30,0))),INDEX(Config!$D$19:$D$30,MATCH(B8,Config!$A$19:$A$30,0)),"falta o material em Config"),"")</f>
+        <f>IFERROR(IF(IF(ISNUMBER(INDEX(Config!$D$19:$D$30,MATCH(B8,Config!$A$19:$A$30,0))),AND(INDEX(Config!$D$19:$D$30,MATCH(B8,Config!$A$19:$A$30,0))&gt;=0),FALSE),INDEX(Config!$D$19:$D$30,MATCH(B8,Config!$A$19:$A$30,0)),"falta o material em Config (número ≥ 0)"),"")</f>
         <v>4</v>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="B13" s="28">
-        <f>IF(B12="","",IF(NOT(ISNUMBER(B12)),B12,IF(NOT(ISNUMBER(Config!$B$5)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)),"falta o material",B12/60*Config!$B$5+B11))))</f>
+        <f>IF(B12="","",IF(NOT(ISNUMBER(B12)),B12,IF(NOT(IF(ISNUMBER(Config!$B$5),AND(Config!$B$5&gt;=0),FALSE)),"falta o custo-hora em Config",IF(NOT(IF(ISNUMBER(B11),AND(B11&gt;=0),FALSE)),"falta o material",B12/60*Config!$B$5+B11))))</f>
         <v>130.666666666667</v>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B14" s="26">
-        <f>IF(NOT(ISNUMBER(Config!$B$5)),"falta o custo-hora em Config",IF(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE),Config!$B$5/(1-Config!$B$6-Config!$B$7),"margens inválidas (Config)"))</f>
+        <f>IF(NOT(IF(ISNUMBER(Config!$B$5),Config!$B$5&gt;=0,FALSE)),"falta o custo-hora em Config",IF(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE),Config!$B$5/(1-Config!$B$6-Config!$B$7),"margens inválidas (Config)"))</f>
         <v>338.983050847458</v>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="26">
-        <f>IF(OR(Config!$A$10="",B19=""),"",IF(NOT(IF(ISNUMBER(B19),AND(B19&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D19)),D19,B19*(1-D19))))</f>
+        <f>IF(B19="","",IF(Config!$A$10="","pagador sem nome",IF(NOT(IF(ISNUMBER(B19),AND(B19&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D19)),D19,B19*(1-D19)))))</f>
         <v>380</v>
       </c>
       <c r="F19" s="26">
@@ -1390,7 +1390,7 @@
         <v>0.5753</v>
       </c>
       <c r="N19" s="30" t="str">
-        <f>IF(E19="","",IF(NOT(ISNUMBER(E19)),E19,IF(NOT(ISNUMBER(C19)),C19,IF(AND(C19&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I19)),IF(ISNUMBER(Config!$B$5),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J19&lt;0,"Não cobre o custo cheio",IF(K19&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
+        <f>IF(E19="","",IF(NOT(ISNUMBER(E19)),E19,IF(NOT(ISNUMBER(C19)),C19,IF(AND(C19&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I19)),IF(IF(ISNUMBER(Config!$B$5),Config!$B$5&gt;=0,FALSE),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J19&lt;0,"Não cobre o custo cheio",IF(K19&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
         <v>Cobre custo e margem</v>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
         <v>0.03</v>
       </c>
       <c r="E20" s="26">
-        <f>IF(OR(Config!$A$11="",B20=""),"",IF(NOT(IF(ISNUMBER(B20),AND(B20&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D20)),D20,B20*(1-D20))))</f>
+        <f>IF(B20="","",IF(Config!$A$11="","pagador sem nome",IF(NOT(IF(ISNUMBER(B20),AND(B20&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D20)),D20,B20*(1-D20)))))</f>
         <v>116.4</v>
       </c>
       <c r="F20" s="26">
@@ -1447,7 +1447,7 @@
         <v>-0.525593421052632</v>
       </c>
       <c r="N20" s="30" t="str">
-        <f>IF(E20="","",IF(NOT(ISNUMBER(E20)),E20,IF(NOT(ISNUMBER(C20)),C20,IF(AND(C20&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I20)),IF(ISNUMBER(Config!$B$5),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J20&lt;0,"Não cobre o custo cheio",IF(K20&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
+        <f>IF(E20="","",IF(NOT(ISNUMBER(E20)),E20,IF(NOT(ISNUMBER(C20)),C20,IF(AND(C20&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I20)),IF(IF(ISNUMBER(Config!$B$5),Config!$B$5&gt;=0,FALSE),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J20&lt;0,"Não cobre o custo cheio",IF(K20&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
         <v>Não cobre o custo cheio</v>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
         <v>0.06</v>
       </c>
       <c r="E21" s="26">
-        <f>IF(OR(Config!$A$12="",B21=""),"",IF(NOT(IF(ISNUMBER(B21),AND(B21&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D21)),D21,B21*(1-D21))))</f>
+        <f>IF(B21="","",IF(Config!$A$12="","pagador sem nome",IF(NOT(IF(ISNUMBER(B21),AND(B21&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D21)),D21,B21*(1-D21)))))</f>
         <v>94</v>
       </c>
       <c r="F21" s="26">
@@ -1504,7 +1504,7 @@
         <v>-0.62017197368421</v>
       </c>
       <c r="N21" s="30" t="str">
-        <f>IF(E21="","",IF(NOT(ISNUMBER(E21)),E21,IF(NOT(ISNUMBER(C21)),C21,IF(AND(C21&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I21)),IF(ISNUMBER(Config!$B$5),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J21&lt;0,"Não cobre o custo cheio",IF(K21&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
+        <f>IF(E21="","",IF(NOT(ISNUMBER(E21)),E21,IF(NOT(ISNUMBER(C21)),C21,IF(AND(C21&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I21)),IF(IF(ISNUMBER(Config!$B$5),Config!$B$5&gt;=0,FALSE),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J21&lt;0,"Não cobre o custo cheio",IF(K21&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
         <v>Não cobre o custo cheio</v>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
         <v>0.1</v>
       </c>
       <c r="E22" s="26">
-        <f>IF(OR(Config!$A$13="",B22=""),"",IF(NOT(IF(ISNUMBER(B22),AND(B22&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D22)),D22,B22*(1-D22))))</f>
+        <f>IF(B22="","",IF(Config!$A$13="","pagador sem nome",IF(NOT(IF(ISNUMBER(B22),AND(B22&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D22)),D22,B22*(1-D22)))))</f>
         <v>81</v>
       </c>
       <c r="F22" s="26">
@@ -1561,7 +1561,7 @@
         <v>-0.675531052631579</v>
       </c>
       <c r="N22" s="30" t="str">
-        <f>IF(E22="","",IF(NOT(ISNUMBER(E22)),E22,IF(NOT(ISNUMBER(C22)),C22,IF(AND(C22&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I22)),IF(ISNUMBER(Config!$B$5),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J22&lt;0,"Não cobre o custo cheio",IF(K22&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
+        <f>IF(E22="","",IF(NOT(ISNUMBER(E22)),E22,IF(NOT(ISNUMBER(C22)),C22,IF(AND(C22&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I22)),IF(IF(ISNUMBER(Config!$B$5),Config!$B$5&gt;=0,FALSE),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J22&lt;0,"Não cobre o custo cheio",IF(K22&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
         <v>Não cobre o custo cheio</v>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
         <v/>
       </c>
       <c r="E23" s="26">
-        <f>IF(OR(Config!$A$14="",B23=""),"",IF(NOT(IF(ISNUMBER(B23),AND(B23&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D23)),D23,B23*(1-D23))))</f>
+        <f>IF(B23="","",IF(Config!$A$14="","pagador sem nome",IF(NOT(IF(ISNUMBER(B23),AND(B23&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D23)),D23,B23*(1-D23)))))</f>
         <v/>
       </c>
       <c r="F23" s="26">
@@ -1616,7 +1616,7 @@
         <v/>
       </c>
       <c r="N23" s="30">
-        <f>IF(E23="","",IF(NOT(ISNUMBER(E23)),E23,IF(NOT(ISNUMBER(C23)),C23,IF(AND(C23&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I23)),IF(ISNUMBER(Config!$B$5),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J23&lt;0,"Não cobre o custo cheio",IF(K23&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
+        <f>IF(E23="","",IF(NOT(ISNUMBER(E23)),E23,IF(NOT(ISNUMBER(C23)),C23,IF(AND(C23&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I23)),IF(IF(ISNUMBER(Config!$B$5),Config!$B$5&gt;=0,FALSE),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J23&lt;0,"Não cobre o custo cheio",IF(K23&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
         <v/>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="E24" s="26">
-        <f>IF(OR(Config!$A$15="",B24=""),"",IF(NOT(IF(ISNUMBER(B24),AND(B24&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D24)),D24,B24*(1-D24))))</f>
+        <f>IF(B24="","",IF(Config!$A$15="","pagador sem nome",IF(NOT(IF(ISNUMBER(B24),AND(B24&gt;=0),FALSE)),"valor inválido",IF(NOT(ISNUMBER(D24)),D24,B24*(1-D24)))))</f>
         <v/>
       </c>
       <c r="F24" s="26">
@@ -1671,7 +1671,7 @@
         <v/>
       </c>
       <c r="N24" s="30">
-        <f>IF(E24="","",IF(NOT(ISNUMBER(E24)),E24,IF(NOT(ISNUMBER(C24)),C24,IF(AND(C24&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I24)),IF(ISNUMBER(Config!$B$5),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J24&lt;0,"Não cobre o custo cheio",IF(K24&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
+        <f>IF(E24="","",IF(NOT(ISNUMBER(E24)),E24,IF(NOT(ISNUMBER(C24)),C24,IF(AND(C24&gt;0,NOT(IF(ISNUMBER(Config!$B$8),AND(Config!$B$8&gt;=0),FALSE))),"falta o custo do dinheiro em Config",IF(NOT(IF(AND(ISNUMBER(Config!$B$6),ISNUMBER(Config!$B$7)),AND(Config!$B$6&gt;=0,Config!$B$6&lt;1,Config!$B$7&gt;=0,Config!$B$7&lt;1,Config!$B$6+Config!$B$7&lt;1),FALSE)),"Margens inválidas em Config",IF(NOT(ISNUMBER(I24)),IF(IF(ISNUMBER(Config!$B$5),Config!$B$5&gt;=0,FALSE),"Faltam dados do procedimento em Config","Falta o custo-hora em Config"),IF(J24&lt;0,"Não cobre o custo cheio",IF(K24&lt;Config!$B$7,"Cobre o custo, não a margem mínima","Cobre custo e margem"))))))))</f>
         <v/>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
         <v>26866.58</v>
       </c>
       <c r="E49" s="42">
-        <f>IF(NOT(ISNUMBER($B$13)),IF(ISNUMBER(Config!$B$5),"faltam dados do procedimento","falta o custo-hora"),IF(SUMPRODUCT((B43:B48&lt;&gt;"")*((A43:A48="")+ISTEXT(B43:B48)+ISNUMBER(B43:B48)*(B43:B48&lt;0)&gt;0))&gt;0,"atendimentos inválidos ou sem pagador",SUM(E43:E48)))</f>
+        <f>IF(NOT(ISNUMBER($B$13)),IF(IF(ISNUMBER(Config!$B$5),Config!$B$5&gt;=0,FALSE),"faltam dados do procedimento","falta o custo-hora"),IF(SUMPRODUCT((B43:B48&lt;&gt;"")*((A43:A48="")+ISTEXT(B43:B48)+ISNUMBER(B43:B48)*(B43:B48&lt;0)&gt;0))&gt;0,"atendimentos inválidos ou sem pagador",SUM(E43:E48)))</f>
         <v>16986.6666666667</v>
       </c>
       <c r="F49" s="42">
@@ -2711,7 +2711,7 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="C19:C30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
@@ -2721,6 +2721,9 @@
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Percentual" error="Margem entre 0 % e 99 %, e impostos + margem abaixo de 100 %." type="custom">
       <formula1>=IF(ISNUMBER(B7),AND(B7&gt;=0,B7&lt;1,B7+N(B6)&lt;1),FALSE)</formula1>
     </dataValidation>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Custo-hora" error="Número maior ou igual a zero." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
